--- a/app/public/wp-content/themes/bookingroom/TestCases_BookingRoom.xlsx
+++ b/app/public/wp-content/themes/bookingroom/TestCases_BookingRoom.xlsx
@@ -1,18 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12030" activeTab="1"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="📊 Tổng quan" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="📋 Danh sách Test Case" state="visible" r:id="rId5"/>
+    <sheet name="📊 Tổng quan" sheetId="1" r:id="rId1"/>
+    <sheet name="📋 Danh sách Test Case" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'📋 Danh sách Test Case'!$A$1:$L$101</definedName>
+  </definedNames>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1241" uniqueCount="684">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1240" uniqueCount="684">
   <si>
     <t>BÁO CÁO TỔNG QUAN KIỂM THỬ - DỰ ÁN BOOKINGROOM</t>
   </si>
@@ -137,7 +143,7 @@
     <t>Website đã deploy, có kết nối internet</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Mở trình duyệt
+    <t>1. Mở trình duyệt
 2. Nhập URL trang chủ
 3. Nhấn Enter</t>
   </si>
@@ -166,7 +172,7 @@
     <t>Trang chủ đã load xong</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Quan sát hero banner
+    <t>1. Quan sát hero banner
 2. Chờ khoảng 5-7 giây</t>
   </si>
   <si>
@@ -188,7 +194,7 @@
     <t>Trang chủ đã load</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Nhìn vào menu chính
+    <t>1. Nhìn vào menu chính
 2. Click lần lượt các mục menu</t>
   </si>
   <si>
@@ -210,7 +216,7 @@
     <t>Trình duyệt ở chế độ mobile (&lt;768px)</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Thu nhỏ cửa sổ trình duyệt dưới 768px
+    <t>1. Thu nhỏ cửa sổ trình duyệt dưới 768px
 2. Tìm nút hamburger
 3. Click nút hamburger</t>
   </si>
@@ -233,7 +239,7 @@
     <t>Website hỗ trợ đa ngôn ngữ</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Tìm nút chuyển ngôn ngữ
+    <t>1. Tìm nút chuyển ngôn ngữ
 2. Click 'EN'
 3. Quan sát nội dung</t>
   </si>
@@ -259,7 +265,7 @@
     <t>Truy cập trang /dat-phong</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Mở trang đặt phòng
+    <t>1. Mở trang đặt phòng
 2. Kiểm tra các trường form</t>
   </si>
   <si>
@@ -281,7 +287,7 @@
     <t>Form đặt phòng hiển thị</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Click vào ô 'Ngày nhận phòng'
+    <t>1. Click vào ô 'Ngày nhận phòng'
 2. Chọn ngày hôm nay</t>
   </si>
   <si>
@@ -300,7 +306,7 @@
     <t>Không cho chọn ngày trong quá khứ</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Click vào ô 'Ngày nhận phòng'
+    <t>1. Click vào ô 'Ngày nhận phòng'
 2. Thử chọn ngày hôm qua</t>
   </si>
   <si>
@@ -322,7 +328,7 @@
     <t>Đã chọn ngày check-in</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Chọn ngày check-in (ví dụ: 20/08/2026)
+    <t>1. Chọn ngày check-in (ví dụ: 20/08/2026)
 2. Quan sát ngày check-out</t>
   </si>
   <si>
@@ -341,7 +347,7 @@
     <t>Dropdown Adults hiển thị đúng tùy chọn</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Click dropdown 'Người lớn'
+    <t>1. Click dropdown 'Người lớn'
 2. Xem các tùy chọn</t>
   </si>
   <si>
@@ -357,7 +363,7 @@
     <t>Dropdown Children hiển thị đúng tùy chọn</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Click dropdown 'Trẻ em'
+    <t>1. Click dropdown 'Trẻ em'
 2. Xem các tùy chọn</t>
   </si>
   <si>
@@ -376,7 +382,7 @@
     <t>Đã điền đầy đủ thông tin</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Chọn check-in: 2026-08-20
+    <t>1. Chọn check-in: 2026-08-20
 2. Chọn check-out: 2026-08-22
 3. Adults: 2, Children: 0
 4. Click 'Kiểm tra phòng trống'</t>
@@ -400,7 +406,7 @@
     <t>Form đặt phòng rỗng</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Không nhập ngày
+    <t>1. Không nhập ngày
 2. Click 'Kiểm tra phòng trống'</t>
   </si>
   <si>
@@ -422,7 +428,7 @@
     <t>Form đã điền đầy đủ</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Click 'Kiểm tra phòng trống'
+    <t>1. Click 'Kiểm tra phòng trống'
 2. Quan sát ngay sau click</t>
   </si>
   <si>
@@ -447,7 +453,7 @@
     <t>Truy cập trang /tim-phong</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Mở trang tìm phòng
+    <t>1. Mở trang tìm phòng
 2. Kiểm tra các trường form</t>
   </si>
   <si>
@@ -469,7 +475,7 @@
     <t>Form tìm phòng hiển thị</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Click nút '+' ở Adults
+    <t>1. Click nút '+' ở Adults
 2. Click nút '-' ở Adults</t>
   </si>
   <si>
@@ -488,7 +494,7 @@
     <t>Nút +/- điều chỉnh số trẻ em</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Click nút '+' ở Children
+    <t>1. Click nút '+' ở Children
 2. Click nút '-' ở Children</t>
   </si>
   <si>
@@ -507,7 +513,7 @@
     <t>Không vượt quá 10 người</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Click '+' ở Adults liên tục cho đến 10
+    <t>1. Click '+' ở Adults liên tục cho đến 10
 2. Click '+' thêm một lần nữa</t>
   </si>
   <si>
@@ -574,7 +580,7 @@
     <t>Có ít nhất 2 loại phòng trong hệ thống</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Click dropdown 'Loại phòng'
+    <t>1. Click dropdown 'Loại phòng'
 2. Chọn một loại phòng cụ thể
 3. Click 'Tìm phòng trống'</t>
   </si>
@@ -615,7 +621,7 @@
     <t>Có phòng còn trống trong khoảng ngày tìm kiếm</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Điền ngày hợp lệ
+    <t>1. Điền ngày hợp lệ
 2. Click 'Tìm phòng trống'</t>
   </si>
   <si>
@@ -637,7 +643,7 @@
     <t>Tất cả phòng đã được đặt trong khoảng ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Điền ngày đã full booking
+    <t>1. Điền ngày đã full booking
 2. Click 'Tìm phòng trống'</t>
   </si>
   <si>
@@ -659,7 +665,7 @@
     <t>Form đã điền hợp lệ</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Click 'Tìm phòng trống'
+    <t>1. Click 'Tìm phòng trống'
 2. Quan sát ngay sau click</t>
   </si>
   <si>
@@ -681,7 +687,7 @@
     <t>Có ít nhất 1 phòng đã publish</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Click vào một phòng
+    <t>1. Click vào một phòng
 2. Quan sát trang chi tiết</t>
   </si>
   <si>
@@ -703,7 +709,7 @@
     <t>Đang ở trang chi tiết phòng</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Quan sát breadcrumb
+    <t>1. Quan sát breadcrumb
 2. Click 'Phòng' trong breadcrumb</t>
   </si>
   <si>
@@ -722,7 +728,7 @@
     <t>Trang chi tiết phòng đã load</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Click vào slot phòng '101'
+    <t>1. Click vào slot phòng '101'
 2. Click lại vào slot phòng '101'</t>
   </si>
   <si>
@@ -744,7 +750,7 @@
     <t>Có phòng đã được đặt (103, 106, 204 theo mặc định)</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Quan sát slot phòng đã đặt
+    <t>1. Quan sát slot phòng đã đặt
 2. Thử click vào slot đó</t>
   </si>
   <si>
@@ -766,7 +772,7 @@
     <t>Trang chi tiết phòng, có nhiều slot phòng trống</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Click phòng 101
+    <t>1. Click phòng 101
 2. Click phòng 102
 3. Quan sát sidebar</t>
   </si>
@@ -789,7 +795,7 @@
     <t>Trang chi tiết phòng</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Click ngày nhận phòng trong sidebar
+    <t>1. Click ngày nhận phòng trong sidebar
 2. Chọn ngày
 3. Click ngày trả phòng
 4. Chọn ngày</t>
@@ -813,7 +819,7 @@
     <t>Đã chọn 1 phòng, đã nhập ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Chọn 1 phòng
+    <t>1. Chọn 1 phòng
 2. Chọn check-in: 20/08, check-out: 22/08 (2 đêm)
 3. Quan sát sidebar</t>
   </si>
@@ -836,7 +842,7 @@
     <t>Trang chi tiết phòng, chưa chọn phòng</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Quan sát nút 'Tiếp tục thanh toán'
+    <t>1. Quan sát nút 'Tiếp tục thanh toán'
 2. Thử click</t>
   </si>
   <si>
@@ -858,7 +864,7 @@
     <t>Đã chọn ít nhất 1 phòng</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Click chọn phòng 101
+    <t>1. Click chọn phòng 101
 2. Quan sát nút</t>
   </si>
   <si>
@@ -880,7 +886,7 @@
     <t>Đã chọn phòng, nhập ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Nhập Họ tên
+    <t>1. Nhập Họ tên
 2. Nhập Số điện thoại
 3. Nhập Email
 4. Nhập Ghi chú (tùy chọn)
@@ -905,7 +911,7 @@
     <t>Đã chọn phòng</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Bỏ trống Họ tên
+    <t>1. Bỏ trống Họ tên
 2. Điền SĐT và Email
 3. Click 'Tiếp tục thanh toán'</t>
   </si>
@@ -925,7 +931,7 @@
     <t>Validate khi thiếu số điện thoại</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Điền tên
+    <t>1. Điền tên
 2. Bỏ trống SĐT
 3. Điền Email
 4. Click đặt phòng</t>
@@ -943,7 +949,7 @@
     <t>Validate khi thiếu email</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Điền tên và SĐT
+    <t>1. Điền tên và SĐT
 2. Bỏ trống Email
 3. Click đặt phòng</t>
   </si>
@@ -1005,7 +1011,7 @@
     <t>Có booking với SĐT 0901234567 và booking_id 123</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Nhập SĐT: 0901234567
+    <t>1. Nhập SĐT: 0901234567
 2. Nhập Mã đặt phòng: 123
 3. Click 'Tra cứu ngay'</t>
   </si>
@@ -1025,7 +1031,7 @@
     <t>Thông báo lỗi khi SĐT sai</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Nhập SĐT sai: 0000000000
+    <t>1. Nhập SĐT sai: 0000000000
 2. Nhập Mã đặt phòng: 123
 3. Click 'Tra cứu ngay'</t>
   </si>
@@ -1045,7 +1051,7 @@
     <t>Thông báo lỗi khi mã booking sai</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Nhập SĐT đúng
+    <t>1. Nhập SĐT đúng
 2. Nhập mã sai: 9999
 3. Click 'Tra cứu ngay'</t>
   </si>
@@ -1068,7 +1074,7 @@
     <t>Form tra cứu hiển thị</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Không nhập gì
+    <t>1. Không nhập gì
 2. Click 'Tra cứu ngay'</t>
   </si>
   <si>
@@ -1087,7 +1093,7 @@
     <t>Lỗi khi thiếu mã booking</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Nhập SĐT: 0901234567
+    <t>1. Nhập SĐT: 0901234567
 2. Không nhập mã
 3. Click 'Tra cứu ngay'</t>
   </si>
@@ -1104,7 +1110,7 @@
     <t>Spinner xuất hiện trong khi gọi API</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Click 'Tra cứu ngay'
+    <t>1. Click 'Tra cứu ngay'
 2. Quan sát ngay sau click</t>
   </si>
   <si>
@@ -1123,7 +1129,7 @@
     <t>Mất kết nối internet</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Tắt internet
+    <t>1. Tắt internet
 2. Nhập đầy đủ thông tin
 3. Click 'Tra cứu ngay'</t>
   </si>
@@ -1230,7 +1236,7 @@
     <t>Trang liên hệ đã load, server email hoạt động</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Nhập Họ tên
+    <t>1. Nhập Họ tên
 2. Nhập Email
 3. Nhập SĐT (tùy chọn)
 4. Nhập Chủ đề (tùy chọn)
@@ -1256,7 +1262,7 @@
     <t>Trang liên hệ</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Bỏ trống Họ tên
+    <t>1. Bỏ trống Họ tên
 2. Nhập Email và Lời nhắn
 3. Submit</t>
   </si>
@@ -1276,7 +1282,7 @@
     <t>Validate trường Email bắt buộc</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Nhập Họ tên và Lời nhắn
+    <t>1. Nhập Họ tên và Lời nhắn
 2. Bỏ trống Email
 3. Submit</t>
   </si>
@@ -1293,7 +1299,7 @@
     <t>Validate trường Lời nhắn bắt buộc</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Nhập Họ tên và Email
+    <t>1. Nhập Họ tên và Email
 2. Bỏ trống Lời nhắn
 3. Submit</t>
   </si>
@@ -1310,7 +1316,7 @@
     <t>Validate định dạng Email</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Nhập Email không đúng định dạng
+    <t>1. Nhập Email không đúng định dạng
 2. Submit</t>
   </si>
   <si>
@@ -1332,7 +1338,7 @@
     <t>Submit form thiếu thông tin</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Nhập Họ tên và Email
+    <t>1. Nhập Họ tên và Email
 2. Bỏ trống Lời nhắn
 3. Submit
 4. Quan sát form</t>
@@ -1356,7 +1362,7 @@
     <t>Google Maps API Key đã được cài đặt trong Customizer</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Mở trang liên hệ
+    <t>1. Mở trang liên hệ
 2. Scroll xuống phần bản đồ</t>
   </si>
   <si>
@@ -1378,7 +1384,7 @@
     <t>Trang liên hệ, social links đã cấu hình</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Click icon Facebook
+    <t>1. Click icon Facebook
 2. Kiểm tra URL mở ra</t>
   </si>
   <si>
@@ -1403,7 +1409,7 @@
     <t>Website load xong, delay = 5 giây (mặc định)</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Mở bất kỳ trang nào
+    <t>1. Mở bất kỳ trang nào
 2. Chờ 5 giây</t>
   </si>
   <si>
@@ -1425,7 +1431,7 @@
     <t>Popup chưa mở</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Tìm nút 'TƯ VẤN' góc phải màn hình
+    <t>1. Tìm nút 'TƯ VẤN' góc phải màn hình
 2. Click vào nút</t>
   </si>
   <si>
@@ -1459,7 +1465,7 @@
     <t>Gửi form tư vấn với đủ thông tin</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Nhập Họ tên: Nguyễn Văn A
+    <t>1. Nhập Họ tên: Nguyễn Văn A
 2. Nhập SĐT: 0901234567
 3. Nhập Email (tùy chọn)
 4. Nhập Lời nhắn (tùy chọn)
@@ -1481,7 +1487,7 @@
     <t>Validate Họ tên bắt buộc</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Bỏ trống Họ tên
+    <t>1. Bỏ trống Họ tên
 2. Nhập SĐT
 3. Submit</t>
   </si>
@@ -1501,7 +1507,7 @@
     <t>Validate SĐT bắt buộc</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Nhập Họ tên
+    <t>1. Nhập Họ tên
 2. Bỏ trống SĐT
 3. Submit</t>
   </si>
@@ -1521,7 +1527,7 @@
     <t>Validate định dạng SĐT</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Nhập Họ tên
+    <t>1. Nhập Họ tên
 2. Nhập SĐT: 'abc123'
 3. Submit</t>
   </si>
@@ -1544,7 +1550,7 @@
     <t>Popup, form hợp lệ</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Điền đầy đủ thông tin
+    <t>1. Điền đầy đủ thông tin
 2. Click 'Gửi Đăng Ký'
 3. Quan sát ngay sau click</t>
   </si>
@@ -1564,7 +1570,7 @@
     <t>Đã gửi form tư vấn thành công</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Gửi form tư vấn
+    <t>1. Gửi form tư vấn
 2. Vào WordPress Admin &gt; Tư vấn Leads</t>
   </si>
   <si>
@@ -1583,7 +1589,7 @@
     <t>Email admin đã cấu hình, form tư vấn gửi thành công</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Gửi form tư vấn
+    <t>1. Gửi form tư vấn
 2. Kiểm tra email admin</t>
   </si>
   <si>
@@ -1671,7 +1677,7 @@
     <t>Đã chọn phương thức thanh toán</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Chọn phương thức
+    <t>1. Chọn phương thức
 2. Click 'Proceed to Payment'</t>
   </si>
   <si>
@@ -1717,7 +1723,7 @@
     <t>Có phòng với capacity=2 và phòng với capacity=4</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Tìm phòng với adults=4, children=0
+    <t>1. Tìm phòng với adults=4, children=0
 2. Kiểm tra kết quả</t>
   </si>
   <si>
@@ -1739,7 +1745,7 @@
     <t>Phòng có cài đặt giá cuối tuần khác giá bình thường</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Tìm phòng với ngày bao gồm cuối tuần
+    <t>1. Tìm phòng với ngày bao gồm cuối tuần
 2. So sánh giá với ngày thường</t>
   </si>
   <si>
@@ -1761,7 +1767,7 @@
     <t>Có mix phòng trống và đã đặt</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Tìm phòng
+    <t>1. Tìm phòng
 2. Kiểm tra thứ tự kết quả</t>
   </si>
   <si>
@@ -1780,7 +1786,7 @@
     <t>Form tìm phòng</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Gọi AJAX không có nonce
+    <t>1. Gọi AJAX không có nonce
 2. Gọi AJAX với nonce sai</t>
   </si>
   <si>
@@ -1802,7 +1808,7 @@
     <t>Trang phòng hiển thị tất cả phòng publish</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Truy cập trang /phong
+    <t>1. Truy cập trang /phong
 2. Quan sát danh sách</t>
   </si>
   <si>
@@ -1863,7 +1869,7 @@
     <t>Trang có nội dung dài hơn viewport</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Cuộn trang xuống
+    <t>1. Cuộn trang xuống
 2. Quan sát header</t>
   </si>
   <si>
@@ -1885,7 +1891,7 @@
     <t>Cuộn xuống cuối trang</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Scroll xuống cuối trang
+    <t>1. Scroll xuống cuối trang
 2. Quan sát footer</t>
   </si>
   <si>
@@ -1901,7 +1907,7 @@
     <t>Tất cả form POST đều có nonce verification</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Inspect form HTML
+    <t>1. Inspect form HTML
 2. Kiểm tra wp_nonce_field
 3. Thử submit form không có nonce</t>
   </si>
@@ -1921,7 +1927,7 @@
     <t>Dữ liệu đầu vào được sanitize</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Nhập HTML script vào form liên hệ
+    <t>1. Nhập HTML script vào form liên hệ
 2. Submit
 3. Kiểm tra dữ liệu được lưu</t>
   </si>
@@ -1944,7 +1950,7 @@
     <t>Server hoạt động bình thường</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Mở DevTools &gt; Network
+    <t>1. Mở DevTools &gt; Network
 2. Hard reload trang chủ</t>
   </si>
   <si>
@@ -1957,7 +1963,7 @@
     <t>Trang chủ tải trong vòng 3 giây trên kết nối 4G</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Mở DevTools
+    <t>1. Mở DevTools
 2. Vào tab Network
 3. Hard reload trang chủ</t>
   </si>
@@ -1983,7 +1989,7 @@
     <t>Đang dùng Tiếng Việt</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Click nút chuyển ngôn ngữ sang EN
+    <t>1. Click nút chuyển ngôn ngữ sang EN
 2. Duyệt các trang</t>
   </si>
   <si>
@@ -2005,7 +2011,7 @@
     <t>Đang dùng tiếng Anh</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Click nút chuyển sang VI
+    <t>1. Click nút chuyển sang VI
 2. Quan sát nội dung</t>
   </si>
   <si>
@@ -2024,7 +2030,7 @@
     <t>Thông báo lỗi hiển thị đúng ngôn ngữ</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Submit form liên hệ trống
+    <t>1. Submit form liên hệ trống
 2. Quan sát thông báo lỗi</t>
   </si>
   <si>
@@ -2043,7 +2049,7 @@
     <t>Website hiển thị đúng trên màn hình 360px</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Mở DevTools
+    <t>1. Mở DevTools
 2. Set viewport width = 360px
 3. Duyệt các trang chính</t>
   </si>
@@ -2063,7 +2069,7 @@
     <t>Website hiển thị đúng trên màn hình 768px</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Set viewport = 768px
+    <t>1. Set viewport = 768px
 2. Duyệt các trang chính</t>
   </si>
   <si>
@@ -2082,7 +2088,7 @@
     <t>Website hiển thị đúng trên màn hình lớn</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Set viewport = 1280px
+    <t>1. Set viewport = 1280px
 2. Duyệt các trang chính</t>
   </si>
   <si>
@@ -2101,7 +2107,7 @@
     <t>Form đặt phòng dùng được trên mobile</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Mở trang đặt phòng trên mobile
+    <t>1. Mở trang đặt phòng trên mobile
 2. Điền form
 3. Submit</t>
   </si>
@@ -2124,7 +2130,7 @@
     <t>Đăng nhập với quyền Admin</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Vào Admin &gt; Phòng &gt; Thêm mới
+    <t>1. Vào Admin &gt; Phòng &gt; Thêm mới
 2. Điền đầy đủ thông tin
 3. Publish</t>
   </si>
@@ -2180,7 +2186,7 @@
     <t>Đăng nhập Admin</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Giao diện &gt; Tuỳ chỉnh
+    <t>1. Giao diện &gt; Tuỳ chỉnh
 2. Sửa số hotline
 3. Publish
 4. Kiểm tra frontend</t>
@@ -2199,18 +2205,18 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="14"/>
       <color rgb="FFFFFFFF"/>
-      <sz val="14"/>
       <name val="Segoe UI"/>
     </font>
     <font>
@@ -2224,40 +2230,53 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <name val="Segoe UI"/>
     </font>
     <font>
-      <b/>
-      <name val="Segoe UI"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Segoe UI"/>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF991B1B"/>
-      <sz val="10"/>
-      <name val="Segoe UI"/>
-    </font>
-    <font>
-      <color rgb="FF475569"/>
-      <sz val="10"/>
-      <name val="Segoe UI"/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF92400E"/>
-      <sz val="10"/>
-      <name val="Segoe UI"/>
+      <sz val="12"/>
+      <color rgb="FF991B1B"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF475569"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
+      <sz val="12"/>
+      <color rgb="FF92400E"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <color rgb="FF166534"/>
-      <sz val="10"/>
-      <name val="Segoe UI"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="9">
@@ -2347,9 +2366,6 @@
   </cellStyleXfs>
   <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2362,7 +2378,13 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2374,10 +2396,10 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2386,13 +2408,10 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2423,44 +2442,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -2490,12 +2509,12 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -2534,439 +2553,398 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:F26"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="4" width="16" customWidth="1"/>
+    <col min="3" max="3" width="32.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="32" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="2:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="2" t="s">
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+    </row>
+    <row r="4" spans="2:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="2" t="s">
+    <row r="5" spans="2:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="2" t="s">
+    <row r="6" spans="2:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="2" t="s">
+    <row r="7" spans="2:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="4" t="s">
+    <row r="9" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="5" t="s">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="4">
         <v>65</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="5">
         <f>C10/C13</f>
-      </c>
-    </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="5" t="s">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="4">
         <v>26</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="5">
         <f>C11/C13</f>
-      </c>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="5" t="s">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B12" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="4">
         <v>9</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="5">
         <f>C12/C13</f>
-      </c>
-    </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B13" s="7" t="s">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B13" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="6">
         <f>SUM(C10:C12)</f>
-      </c>
-      <c r="D13" s="8">
+        <v>100</v>
+      </c>
+      <c r="D13" s="7">
         <f>SUM(D10:D12)</f>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B15" s="9" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="8" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B16" s="5" t="s">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B16" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="4">
         <v>58</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="5">
         <f>C16/C26</f>
+        <v>0.57999999999999996</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C17" s="4">
         <v>17</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="5">
         <f>C17/C26</f>
+        <v>0.17</v>
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C18" s="4">
         <v>9</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="5">
         <f>C18/C26</f>
+        <v>0.09</v>
       </c>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="5">
+      <c r="C19" s="4">
         <v>5</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="5">
         <f>C19/C26</f>
+        <v>0.05</v>
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="5">
+      <c r="C20" s="4">
         <v>3</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="5">
         <f>C20/C26</f>
+        <v>0.03</v>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="5">
+      <c r="C21" s="4">
         <v>3</v>
       </c>
-      <c r="D21" s="6">
+      <c r="D21" s="5">
         <f>C21/C26</f>
+        <v>0.03</v>
       </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="5">
+      <c r="C22" s="4">
         <v>2</v>
       </c>
-      <c r="D22" s="6">
+      <c r="D22" s="5">
         <f>C22/C26</f>
+        <v>0.02</v>
       </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="5">
+      <c r="C23" s="4">
         <v>1</v>
       </c>
-      <c r="D23" s="6">
+      <c r="D23" s="5">
         <f>C23/C26</f>
+        <v>0.01</v>
       </c>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="5">
+      <c r="C24" s="4">
         <v>1</v>
       </c>
-      <c r="D24" s="6">
+      <c r="D24" s="5">
         <f>C24/C26</f>
+        <v>0.01</v>
       </c>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="5">
+      <c r="C25" s="4">
         <v>1</v>
       </c>
-      <c r="D25" s="6">
+      <c r="D25" s="5">
         <f>C25/C26</f>
-      </c>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B26" s="7" t="s">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B26" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C26" s="6">
         <f>SUM(C16:C25)</f>
-      </c>
-      <c r="D26" s="8">
+        <v>100</v>
+      </c>
+      <c r="D26" s="7">
         <f>SUM(D16:D25)</f>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2974,18 +2952,18 @@
     <mergeCell ref="B2:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L101"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="3" max="3" width="33.140625" customWidth="1"/>
     <col min="4" max="4" width="36" customWidth="1"/>
     <col min="5" max="5" width="28" customWidth="1"/>
     <col min="6" max="6" width="44" customWidth="1"/>
@@ -2997,3847 +2975,3845 @@
     <col min="12" max="12" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:12" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="L1" s="11" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+    <row r="2" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="I2" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="J2" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="K2" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L2" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="3" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
+      <c r="K2" s="16"/>
+      <c r="L2" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="G3" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="H3" s="18" t="s">
+      <c r="H3" s="10" t="s">
         <v>52</v>
       </c>
       <c r="I3" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="J3" s="16" t="s">
+      <c r="J3" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L3" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
+      <c r="K3" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L3" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="G4" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="H4" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="I4" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="K4" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L4" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
+      <c r="K4" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L4" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A5" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="G5" s="18" t="s">
+      <c r="G5" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="H5" s="18" t="s">
+      <c r="H5" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="I5" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J5" s="16" t="s">
+      <c r="J5" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="K5" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L5" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="6" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
+      <c r="K5" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L5" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="H6" s="13" t="s">
+      <c r="H6" s="14" t="s">
         <v>73</v>
       </c>
       <c r="I6" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="J6" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="K6" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L6" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
+      <c r="K6" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L6" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="G7" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="H7" s="18" t="s">
+      <c r="H7" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="I7" s="14" t="s">
+      <c r="I7" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="16" t="s">
+      <c r="J7" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="K7" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L7" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
+      <c r="K7" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L7" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="F8" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="G8" s="13" t="s">
+      <c r="G8" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="H8" s="13" t="s">
+      <c r="H8" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="I8" s="14" t="s">
+      <c r="I8" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J8" s="11" t="s">
+      <c r="J8" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="K8" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L8" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="16" t="s">
+      <c r="K8" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L8" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F9" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="G9" s="18" t="s">
+      <c r="G9" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="H9" s="18" t="s">
+      <c r="H9" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="I9" s="14" t="s">
+      <c r="I9" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J9" s="16" t="s">
+      <c r="J9" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="K9" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L9" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
+      <c r="K9" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L9" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="F10" s="13" t="s">
+      <c r="F10" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="G10" s="13" t="s">
+      <c r="G10" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="H10" s="13" t="s">
+      <c r="H10" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="I10" s="14" t="s">
+      <c r="I10" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J10" s="11" t="s">
+      <c r="J10" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="K10" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L10" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="16" t="s">
+      <c r="K10" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L10" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="F11" s="18" t="s">
+      <c r="F11" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="G11" s="18" t="s">
+      <c r="G11" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="H11" s="18" t="s">
+      <c r="H11" s="10" t="s">
         <v>106</v>
       </c>
       <c r="I11" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="J11" s="16" t="s">
+      <c r="J11" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L11" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
+      <c r="K11" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L11" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="E12" s="13" t="s">
+      <c r="E12" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="F12" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="G12" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="H12" s="13" t="s">
+      <c r="H12" s="14" t="s">
         <v>111</v>
       </c>
       <c r="I12" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="J12" s="11" t="s">
+      <c r="J12" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="K12" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L12" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="13" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
+      <c r="K12" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L12" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="E13" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="F13" s="18" t="s">
+      <c r="F13" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="G13" s="18" t="s">
+      <c r="G13" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="H13" s="18" t="s">
+      <c r="H13" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="I13" s="14" t="s">
+      <c r="I13" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J13" s="16" t="s">
+      <c r="J13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="K13" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L13" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="14" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
+      <c r="K13" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L13" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="E14" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="F14" s="13" t="s">
+      <c r="F14" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="G14" s="13" t="s">
+      <c r="G14" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="H14" s="13" t="s">
+      <c r="H14" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="I14" s="14" t="s">
+      <c r="I14" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J14" s="11" t="s">
+      <c r="J14" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="K14" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L14" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="15" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="16" t="s">
+      <c r="K14" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L14" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="D15" s="18" t="s">
+      <c r="D15" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="E15" s="18" t="s">
+      <c r="E15" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="F15" s="18" t="s">
+      <c r="F15" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="G15" s="18" t="s">
+      <c r="G15" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="H15" s="18" t="s">
+      <c r="H15" s="10" t="s">
         <v>132</v>
       </c>
       <c r="I15" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="J15" s="16" t="s">
+      <c r="J15" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="K15" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L15" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
+      <c r="K15" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L15" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D16" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="E16" s="13" t="s">
+      <c r="E16" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="F16" s="13" t="s">
+      <c r="F16" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="G16" s="13" t="s">
+      <c r="G16" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="H16" s="13" t="s">
+      <c r="H16" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="I16" s="14" t="s">
+      <c r="I16" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J16" s="11" t="s">
+      <c r="J16" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="K16" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L16" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="16" t="s">
+      <c r="K16" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L16" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="C17" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="D17" s="18" t="s">
+      <c r="D17" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="E17" s="18" t="s">
+      <c r="E17" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="F17" s="18" t="s">
+      <c r="F17" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="G17" s="18" t="s">
+      <c r="G17" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="H17" s="18" t="s">
+      <c r="H17" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="I17" s="14" t="s">
+      <c r="I17" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J17" s="16" t="s">
+      <c r="J17" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="K17" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L17" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="11" t="s">
+      <c r="K17" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L17" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="E18" s="13" t="s">
+      <c r="E18" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="F18" s="13" t="s">
+      <c r="F18" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="G18" s="13" t="s">
+      <c r="G18" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="H18" s="13" t="s">
+      <c r="H18" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="I18" s="14" t="s">
+      <c r="I18" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J18" s="11" t="s">
+      <c r="J18" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="K18" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L18" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="19" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="16" t="s">
+      <c r="K18" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L18" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="C19" s="17" t="s">
+      <c r="C19" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="D19" s="18" t="s">
+      <c r="D19" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="E19" s="18" t="s">
+      <c r="E19" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="F19" s="18" t="s">
+      <c r="F19" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="G19" s="18" t="s">
+      <c r="G19" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="H19" s="18" t="s">
+      <c r="H19" s="10" t="s">
         <v>159</v>
       </c>
       <c r="I19" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="J19" s="16" t="s">
+      <c r="J19" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="K19" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L19" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="20" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="s">
+      <c r="K19" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L19" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="D20" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="E20" s="13" t="s">
+      <c r="E20" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="F20" s="13" t="s">
+      <c r="F20" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="G20" s="13" t="s">
+      <c r="G20" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="H20" s="13" t="s">
+      <c r="H20" s="14" t="s">
         <v>164</v>
       </c>
       <c r="I20" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="J20" s="11" t="s">
+      <c r="J20" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="K20" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L20" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="21" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
+      <c r="K20" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L20" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="C21" s="17" t="s">
+      <c r="C21" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="D21" s="18" t="s">
+      <c r="D21" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="E21" s="18" t="s">
+      <c r="E21" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="F21" s="18" t="s">
+      <c r="F21" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="G21" s="18" t="s">
+      <c r="G21" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="H21" s="18" t="s">
+      <c r="H21" s="10" t="s">
         <v>169</v>
       </c>
       <c r="I21" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="J21" s="16" t="s">
+      <c r="J21" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="K21" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L21" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="22" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="11" t="s">
+      <c r="K21" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L21" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="B22" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="D22" s="13" t="s">
+      <c r="D22" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="E22" s="13" t="s">
+      <c r="E22" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="F22" s="13" t="s">
+      <c r="F22" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="G22" s="13" t="s">
+      <c r="G22" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="H22" s="13" t="s">
+      <c r="H22" s="14" t="s">
         <v>174</v>
       </c>
       <c r="I22" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="J22" s="11" t="s">
+      <c r="J22" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="K22" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L22" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="23" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="16" t="s">
+      <c r="K22" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L22" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="17" t="s">
         <v>175</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="C23" s="17" t="s">
+      <c r="C23" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="D23" s="18" t="s">
+      <c r="D23" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="E23" s="18" t="s">
+      <c r="E23" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="F23" s="18" t="s">
+      <c r="F23" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="G23" s="18" t="s">
+      <c r="G23" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="H23" s="18" t="s">
+      <c r="H23" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="I23" s="14" t="s">
+      <c r="I23" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J23" s="16" t="s">
+      <c r="J23" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="K23" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L23" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="24" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="11" t="s">
+      <c r="K23" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L23" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="B24" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C24" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="D24" s="13" t="s">
+      <c r="D24" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="E24" s="13" t="s">
+      <c r="E24" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="F24" s="13" t="s">
+      <c r="F24" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="G24" s="13" t="s">
+      <c r="G24" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="H24" s="13" t="s">
+      <c r="H24" s="14" t="s">
         <v>187</v>
       </c>
       <c r="I24" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="J24" s="11" t="s">
+      <c r="J24" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="K24" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L24" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="25" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="16" t="s">
+      <c r="K24" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L24" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="B25" s="17" t="s">
+      <c r="B25" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="C25" s="17" t="s">
+      <c r="C25" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="D25" s="18" t="s">
+      <c r="D25" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="E25" s="18" t="s">
+      <c r="E25" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="F25" s="18" t="s">
+      <c r="F25" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="G25" s="18" t="s">
+      <c r="G25" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="H25" s="18" t="s">
+      <c r="H25" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="I25" s="14" t="s">
+      <c r="I25" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J25" s="16" t="s">
+      <c r="J25" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="K25" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L25" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="26" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="11" t="s">
+      <c r="K25" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L25" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="C26" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="D26" s="13" t="s">
+      <c r="D26" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="E26" s="13" t="s">
+      <c r="E26" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="F26" s="13" t="s">
+      <c r="F26" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="G26" s="13" t="s">
+      <c r="G26" s="14" t="s">
         <v>200</v>
       </c>
-      <c r="H26" s="13" t="s">
+      <c r="H26" s="14" t="s">
         <v>201</v>
       </c>
-      <c r="I26" s="14" t="s">
+      <c r="I26" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J26" s="11" t="s">
+      <c r="J26" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="K26" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L26" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="27" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="16" t="s">
+      <c r="K26" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L26" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="17" t="s">
         <v>202</v>
       </c>
-      <c r="B27" s="17" t="s">
+      <c r="B27" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="C27" s="17" t="s">
+      <c r="C27" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="D27" s="18" t="s">
+      <c r="D27" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="E27" s="18" t="s">
+      <c r="E27" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="F27" s="18" t="s">
+      <c r="F27" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="G27" s="18" t="s">
+      <c r="G27" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="H27" s="18" t="s">
+      <c r="H27" s="10" t="s">
         <v>207</v>
       </c>
       <c r="I27" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="J27" s="16" t="s">
+      <c r="J27" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="K27" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L27" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="28" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="11" t="s">
+      <c r="K27" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L27" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="B28" s="12" t="s">
+      <c r="B28" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="C28" s="12" t="s">
+      <c r="C28" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="D28" s="13" t="s">
+      <c r="D28" s="14" t="s">
         <v>211</v>
       </c>
-      <c r="E28" s="13" t="s">
+      <c r="E28" s="14" t="s">
         <v>212</v>
       </c>
-      <c r="F28" s="13" t="s">
+      <c r="F28" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="G28" s="13" t="s">
+      <c r="G28" s="14" t="s">
         <v>214</v>
       </c>
-      <c r="H28" s="13" t="s">
+      <c r="H28" s="14" t="s">
         <v>215</v>
       </c>
-      <c r="I28" s="14" t="s">
+      <c r="I28" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J28" s="11" t="s">
+      <c r="J28" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="K28" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L28" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="29" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="16" t="s">
+      <c r="K28" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L28" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="17" t="s">
         <v>216</v>
       </c>
-      <c r="B29" s="17" t="s">
+      <c r="B29" s="18" t="s">
         <v>209</v>
       </c>
-      <c r="C29" s="17" t="s">
+      <c r="C29" s="18" t="s">
         <v>217</v>
       </c>
-      <c r="D29" s="18" t="s">
+      <c r="D29" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="E29" s="18" t="s">
+      <c r="E29" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="F29" s="18" t="s">
+      <c r="F29" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="G29" s="18" t="s">
+      <c r="G29" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="H29" s="18" t="s">
+      <c r="H29" s="10" t="s">
         <v>221</v>
       </c>
       <c r="I29" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="J29" s="16" t="s">
+      <c r="J29" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="K29" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L29" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="30" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="11" t="s">
+      <c r="K29" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L29" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="12" t="s">
         <v>222</v>
       </c>
-      <c r="B30" s="12" t="s">
+      <c r="B30" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="C30" s="13" t="s">
         <v>223</v>
       </c>
-      <c r="D30" s="13" t="s">
+      <c r="D30" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="E30" s="13" t="s">
+      <c r="E30" s="14" t="s">
         <v>225</v>
       </c>
-      <c r="F30" s="13" t="s">
+      <c r="F30" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="G30" s="13" t="s">
+      <c r="G30" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="H30" s="13" t="s">
+      <c r="H30" s="14" t="s">
         <v>228</v>
       </c>
-      <c r="I30" s="14" t="s">
+      <c r="I30" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J30" s="11" t="s">
+      <c r="J30" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="K30" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L30" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="31" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="16" t="s">
+      <c r="K30" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L30" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="17" t="s">
         <v>229</v>
       </c>
-      <c r="B31" s="17" t="s">
+      <c r="B31" s="18" t="s">
         <v>209</v>
       </c>
-      <c r="C31" s="17" t="s">
+      <c r="C31" s="18" t="s">
         <v>230</v>
       </c>
-      <c r="D31" s="18" t="s">
+      <c r="D31" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="E31" s="18" t="s">
+      <c r="E31" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="F31" s="18" t="s">
+      <c r="F31" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="G31" s="18" t="s">
+      <c r="G31" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="H31" s="18" t="s">
+      <c r="H31" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="I31" s="14" t="s">
+      <c r="I31" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J31" s="16" t="s">
+      <c r="J31" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="K31" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L31" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="32" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="11" t="s">
+      <c r="K31" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L31" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="C32" s="12" t="s">
+      <c r="C32" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="D32" s="13" t="s">
+      <c r="D32" s="14" t="s">
         <v>238</v>
       </c>
-      <c r="E32" s="13" t="s">
+      <c r="E32" s="14" t="s">
         <v>239</v>
       </c>
-      <c r="F32" s="13" t="s">
+      <c r="F32" s="14" t="s">
         <v>240</v>
       </c>
-      <c r="G32" s="13" t="s">
+      <c r="G32" s="14" t="s">
         <v>241</v>
       </c>
-      <c r="H32" s="13" t="s">
+      <c r="H32" s="14" t="s">
         <v>242</v>
       </c>
-      <c r="I32" s="14" t="s">
+      <c r="I32" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J32" s="11" t="s">
+      <c r="J32" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="K32" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L32" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="33" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="16" t="s">
+      <c r="K32" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L32" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="17" t="s">
         <v>243</v>
       </c>
-      <c r="B33" s="17" t="s">
+      <c r="B33" s="18" t="s">
         <v>209</v>
       </c>
-      <c r="C33" s="17" t="s">
+      <c r="C33" s="18" t="s">
         <v>244</v>
       </c>
-      <c r="D33" s="18" t="s">
+      <c r="D33" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="E33" s="18" t="s">
+      <c r="E33" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="F33" s="18" t="s">
+      <c r="F33" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="G33" s="18" t="s">
+      <c r="G33" s="10" t="s">
         <v>248</v>
       </c>
-      <c r="H33" s="18" t="s">
+      <c r="H33" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="I33" s="14" t="s">
+      <c r="I33" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J33" s="16" t="s">
+      <c r="J33" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="K33" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L33" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="34" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="11" t="s">
+      <c r="K33" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L33" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="12" t="s">
         <v>250</v>
       </c>
-      <c r="B34" s="12" t="s">
+      <c r="B34" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="C34" s="12" t="s">
+      <c r="C34" s="13" t="s">
         <v>251</v>
       </c>
-      <c r="D34" s="13" t="s">
+      <c r="D34" s="14" t="s">
         <v>252</v>
       </c>
-      <c r="E34" s="13" t="s">
+      <c r="E34" s="14" t="s">
         <v>253</v>
       </c>
-      <c r="F34" s="13" t="s">
+      <c r="F34" s="14" t="s">
         <v>254</v>
       </c>
-      <c r="G34" s="13" t="s">
+      <c r="G34" s="14" t="s">
         <v>255</v>
       </c>
-      <c r="H34" s="13" t="s">
+      <c r="H34" s="14" t="s">
         <v>256</v>
       </c>
-      <c r="I34" s="14" t="s">
+      <c r="I34" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J34" s="11" t="s">
+      <c r="J34" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="K34" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L34" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="35" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="16" t="s">
+      <c r="K34" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L34" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="17" t="s">
         <v>257</v>
       </c>
-      <c r="B35" s="17" t="s">
+      <c r="B35" s="18" t="s">
         <v>209</v>
       </c>
-      <c r="C35" s="17" t="s">
+      <c r="C35" s="18" t="s">
         <v>258</v>
       </c>
-      <c r="D35" s="18" t="s">
+      <c r="D35" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="E35" s="18" t="s">
+      <c r="E35" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="F35" s="18" t="s">
+      <c r="F35" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="G35" s="18" t="s">
+      <c r="G35" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="H35" s="18" t="s">
+      <c r="H35" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="I35" s="14" t="s">
+      <c r="I35" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J35" s="16" t="s">
+      <c r="J35" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="K35" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L35" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="36" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="11" t="s">
+      <c r="K35" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L35" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="12" t="s">
         <v>264</v>
       </c>
-      <c r="B36" s="12" t="s">
+      <c r="B36" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="C36" s="12" t="s">
+      <c r="C36" s="13" t="s">
         <v>265</v>
       </c>
-      <c r="D36" s="13" t="s">
+      <c r="D36" s="14" t="s">
         <v>266</v>
       </c>
-      <c r="E36" s="13" t="s">
+      <c r="E36" s="14" t="s">
         <v>267</v>
       </c>
-      <c r="F36" s="13" t="s">
+      <c r="F36" s="14" t="s">
         <v>268</v>
       </c>
-      <c r="G36" s="13" t="s">
+      <c r="G36" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="H36" s="13" t="s">
+      <c r="H36" s="14" t="s">
         <v>270</v>
       </c>
-      <c r="I36" s="14" t="s">
+      <c r="I36" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J36" s="11" t="s">
+      <c r="J36" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="K36" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L36" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="37" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37" s="16" t="s">
+      <c r="K36" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L36" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="17" t="s">
         <v>271</v>
       </c>
-      <c r="B37" s="17" t="s">
+      <c r="B37" s="18" t="s">
         <v>209</v>
       </c>
-      <c r="C37" s="17" t="s">
+      <c r="C37" s="18" t="s">
         <v>272</v>
       </c>
-      <c r="D37" s="18" t="s">
+      <c r="D37" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="E37" s="18" t="s">
+      <c r="E37" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="F37" s="18" t="s">
+      <c r="F37" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="G37" s="18" t="s">
+      <c r="G37" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="H37" s="18" t="s">
+      <c r="H37" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="I37" s="14" t="s">
+      <c r="I37" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J37" s="16" t="s">
+      <c r="J37" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="K37" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L37" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="38" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" s="11" t="s">
+      <c r="K37" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L37" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="12" t="s">
         <v>278</v>
       </c>
-      <c r="B38" s="12" t="s">
+      <c r="B38" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="C38" s="12" t="s">
+      <c r="C38" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="D38" s="13" t="s">
+      <c r="D38" s="14" t="s">
         <v>280</v>
       </c>
-      <c r="E38" s="13" t="s">
+      <c r="E38" s="14" t="s">
         <v>281</v>
       </c>
-      <c r="F38" s="13" t="s">
+      <c r="F38" s="14" t="s">
         <v>282</v>
       </c>
-      <c r="G38" s="13" t="s">
+      <c r="G38" s="14" t="s">
         <v>283</v>
       </c>
-      <c r="H38" s="13" t="s">
+      <c r="H38" s="14" t="s">
         <v>284</v>
       </c>
-      <c r="I38" s="14" t="s">
+      <c r="I38" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J38" s="11" t="s">
+      <c r="J38" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="K38" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L38" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="39" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" s="16" t="s">
+      <c r="K38" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L38" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="17" t="s">
         <v>285</v>
       </c>
-      <c r="B39" s="17" t="s">
+      <c r="B39" s="18" t="s">
         <v>209</v>
       </c>
-      <c r="C39" s="17" t="s">
+      <c r="C39" s="18" t="s">
         <v>286</v>
       </c>
-      <c r="D39" s="18" t="s">
+      <c r="D39" s="10" t="s">
         <v>287</v>
       </c>
-      <c r="E39" s="18" t="s">
+      <c r="E39" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="F39" s="18" t="s">
+      <c r="F39" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="G39" s="18" t="s">
+      <c r="G39" s="10" t="s">
         <v>289</v>
       </c>
-      <c r="H39" s="18" t="s">
+      <c r="H39" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="I39" s="14" t="s">
+      <c r="I39" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J39" s="16" t="s">
+      <c r="J39" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="K39" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L39" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="40" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" s="11" t="s">
+      <c r="K39" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L39" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="12" t="s">
         <v>290</v>
       </c>
-      <c r="B40" s="12" t="s">
+      <c r="B40" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="C40" s="12" t="s">
+      <c r="C40" s="13" t="s">
         <v>291</v>
       </c>
-      <c r="D40" s="13" t="s">
+      <c r="D40" s="14" t="s">
         <v>292</v>
       </c>
-      <c r="E40" s="13" t="s">
+      <c r="E40" s="14" t="s">
         <v>281</v>
       </c>
-      <c r="F40" s="13" t="s">
+      <c r="F40" s="14" t="s">
         <v>293</v>
       </c>
-      <c r="G40" s="13" t="s">
+      <c r="G40" s="14" t="s">
         <v>294</v>
       </c>
-      <c r="H40" s="13" t="s">
+      <c r="H40" s="14" t="s">
         <v>284</v>
       </c>
-      <c r="I40" s="14" t="s">
+      <c r="I40" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J40" s="11" t="s">
+      <c r="J40" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="K40" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L40" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="41" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A41" s="16" t="s">
+      <c r="K40" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L40" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="17" t="s">
         <v>295</v>
       </c>
-      <c r="B41" s="17" t="s">
+      <c r="B41" s="18" t="s">
         <v>209</v>
       </c>
-      <c r="C41" s="17" t="s">
+      <c r="C41" s="18" t="s">
         <v>296</v>
       </c>
-      <c r="D41" s="18" t="s">
+      <c r="D41" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="E41" s="18" t="s">
+      <c r="E41" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F41" s="18" t="s">
+      <c r="F41" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="G41" s="18" t="s">
+      <c r="G41" s="10" t="s">
         <v>299</v>
       </c>
-      <c r="H41" s="18" t="s">
+      <c r="H41" s="10" t="s">
         <v>300</v>
       </c>
       <c r="I41" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="J41" s="16" t="s">
+      <c r="J41" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="K41" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L41" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="42" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42" s="11" t="s">
+      <c r="K41" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L41" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="12" t="s">
         <v>301</v>
       </c>
-      <c r="B42" s="12" t="s">
+      <c r="B42" s="13" t="s">
         <v>302</v>
       </c>
-      <c r="C42" s="12" t="s">
+      <c r="C42" s="13" t="s">
         <v>303</v>
       </c>
-      <c r="D42" s="13" t="s">
+      <c r="D42" s="14" t="s">
         <v>304</v>
       </c>
-      <c r="E42" s="13" t="s">
+      <c r="E42" s="14" t="s">
         <v>305</v>
       </c>
-      <c r="F42" s="13" t="s">
+      <c r="F42" s="14" t="s">
         <v>306</v>
       </c>
-      <c r="G42" s="13" t="s">
+      <c r="G42" s="14" t="s">
         <v>307</v>
       </c>
-      <c r="H42" s="13" t="s">
+      <c r="H42" s="14" t="s">
         <v>308</v>
       </c>
-      <c r="I42" s="14" t="s">
+      <c r="I42" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J42" s="11" t="s">
+      <c r="J42" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="K42" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L42" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="43" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A43" s="16" t="s">
+      <c r="K42" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L42" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="17" t="s">
         <v>309</v>
       </c>
-      <c r="B43" s="17" t="s">
+      <c r="B43" s="18" t="s">
         <v>302</v>
       </c>
-      <c r="C43" s="17" t="s">
+      <c r="C43" s="18" t="s">
         <v>310</v>
       </c>
-      <c r="D43" s="18" t="s">
+      <c r="D43" s="10" t="s">
         <v>311</v>
       </c>
-      <c r="E43" s="18" t="s">
+      <c r="E43" s="10" t="s">
         <v>312</v>
       </c>
-      <c r="F43" s="18" t="s">
+      <c r="F43" s="10" t="s">
         <v>313</v>
       </c>
-      <c r="G43" s="18" t="s">
+      <c r="G43" s="10" t="s">
         <v>314</v>
       </c>
-      <c r="H43" s="18" t="s">
+      <c r="H43" s="10" t="s">
         <v>315</v>
       </c>
-      <c r="I43" s="14" t="s">
+      <c r="I43" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J43" s="16" t="s">
+      <c r="J43" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="K43" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L43" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="44" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A44" s="11" t="s">
+      <c r="K43" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L43" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="12" t="s">
         <v>316</v>
       </c>
-      <c r="B44" s="12" t="s">
+      <c r="B44" s="13" t="s">
         <v>302</v>
       </c>
-      <c r="C44" s="12" t="s">
+      <c r="C44" s="13" t="s">
         <v>317</v>
       </c>
-      <c r="D44" s="13" t="s">
+      <c r="D44" s="14" t="s">
         <v>318</v>
       </c>
-      <c r="E44" s="13" t="s">
+      <c r="E44" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="F44" s="13" t="s">
+      <c r="F44" s="14" t="s">
         <v>319</v>
       </c>
-      <c r="G44" s="13" t="s">
+      <c r="G44" s="14" t="s">
         <v>320</v>
       </c>
-      <c r="H44" s="13" t="s">
+      <c r="H44" s="14" t="s">
         <v>321</v>
       </c>
-      <c r="I44" s="14" t="s">
+      <c r="I44" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J44" s="11" t="s">
+      <c r="J44" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="K44" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L44" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="45" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A45" s="16" t="s">
+      <c r="K44" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L44" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="17" t="s">
         <v>322</v>
       </c>
-      <c r="B45" s="17" t="s">
+      <c r="B45" s="18" t="s">
         <v>302</v>
       </c>
-      <c r="C45" s="17" t="s">
+      <c r="C45" s="18" t="s">
         <v>323</v>
       </c>
-      <c r="D45" s="18" t="s">
+      <c r="D45" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="E45" s="18" t="s">
+      <c r="E45" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F45" s="18" t="s">
+      <c r="F45" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="G45" s="18" t="s">
+      <c r="G45" s="10" t="s">
         <v>326</v>
       </c>
-      <c r="H45" s="18" t="s">
+      <c r="H45" s="10" t="s">
         <v>327</v>
       </c>
-      <c r="I45" s="14" t="s">
+      <c r="I45" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J45" s="16" t="s">
+      <c r="J45" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="K45" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L45" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="46" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A46" s="11" t="s">
+      <c r="K45" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L45" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="12" t="s">
         <v>328</v>
       </c>
-      <c r="B46" s="12" t="s">
+      <c r="B46" s="13" t="s">
         <v>302</v>
       </c>
-      <c r="C46" s="12" t="s">
+      <c r="C46" s="13" t="s">
         <v>329</v>
       </c>
-      <c r="D46" s="13" t="s">
+      <c r="D46" s="14" t="s">
         <v>330</v>
       </c>
-      <c r="E46" s="13" t="s">
+      <c r="E46" s="14" t="s">
         <v>331</v>
       </c>
-      <c r="F46" s="13" t="s">
+      <c r="F46" s="14" t="s">
         <v>332</v>
       </c>
-      <c r="G46" s="13" t="s">
+      <c r="G46" s="14" t="s">
         <v>333</v>
       </c>
-      <c r="H46" s="13" t="s">
+      <c r="H46" s="14" t="s">
         <v>334</v>
       </c>
-      <c r="I46" s="14" t="s">
+      <c r="I46" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J46" s="11" t="s">
+      <c r="J46" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="K46" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L46" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="47" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47" s="16" t="s">
+      <c r="K46" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L46" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="17" t="s">
         <v>335</v>
       </c>
-      <c r="B47" s="17" t="s">
+      <c r="B47" s="18" t="s">
         <v>302</v>
       </c>
-      <c r="C47" s="17" t="s">
+      <c r="C47" s="18" t="s">
         <v>336</v>
       </c>
-      <c r="D47" s="18" t="s">
+      <c r="D47" s="10" t="s">
         <v>337</v>
       </c>
-      <c r="E47" s="18" t="s">
+      <c r="E47" s="10" t="s">
         <v>331</v>
       </c>
-      <c r="F47" s="18" t="s">
+      <c r="F47" s="10" t="s">
         <v>338</v>
       </c>
-      <c r="G47" s="18" t="s">
+      <c r="G47" s="10" t="s">
         <v>339</v>
       </c>
-      <c r="H47" s="18" t="s">
+      <c r="H47" s="10" t="s">
         <v>334</v>
       </c>
-      <c r="I47" s="14" t="s">
+      <c r="I47" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J47" s="16" t="s">
+      <c r="J47" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="K47" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L47" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="48" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A48" s="11" t="s">
+      <c r="K47" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L47" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="12" t="s">
         <v>340</v>
       </c>
-      <c r="B48" s="12" t="s">
+      <c r="B48" s="13" t="s">
         <v>302</v>
       </c>
-      <c r="C48" s="12" t="s">
+      <c r="C48" s="13" t="s">
         <v>341</v>
       </c>
-      <c r="D48" s="13" t="s">
+      <c r="D48" s="14" t="s">
         <v>342</v>
       </c>
-      <c r="E48" s="13" t="s">
+      <c r="E48" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="F48" s="13" t="s">
+      <c r="F48" s="14" t="s">
         <v>343</v>
       </c>
-      <c r="G48" s="13" t="s">
+      <c r="G48" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="H48" s="13" t="s">
+      <c r="H48" s="14" t="s">
         <v>344</v>
       </c>
       <c r="I48" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="J48" s="11" t="s">
+      <c r="J48" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K48" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L48" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="49" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A49" s="16" t="s">
+      <c r="K48" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L48" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="17" t="s">
         <v>345</v>
       </c>
-      <c r="B49" s="17" t="s">
+      <c r="B49" s="18" t="s">
         <v>302</v>
       </c>
-      <c r="C49" s="17" t="s">
+      <c r="C49" s="18" t="s">
         <v>346</v>
       </c>
-      <c r="D49" s="18" t="s">
+      <c r="D49" s="10" t="s">
         <v>347</v>
       </c>
-      <c r="E49" s="18" t="s">
+      <c r="E49" s="10" t="s">
         <v>348</v>
       </c>
-      <c r="F49" s="18" t="s">
+      <c r="F49" s="10" t="s">
         <v>349</v>
       </c>
-      <c r="G49" s="18" t="s">
+      <c r="G49" s="10" t="s">
         <v>350</v>
       </c>
-      <c r="H49" s="18" t="s">
+      <c r="H49" s="10" t="s">
         <v>351</v>
       </c>
       <c r="I49" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="J49" s="16" t="s">
+      <c r="J49" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="K49" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L49" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="50" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A50" s="11" t="s">
+      <c r="K49" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L49" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="12" t="s">
         <v>352</v>
       </c>
-      <c r="B50" s="12" t="s">
+      <c r="B50" s="13" t="s">
         <v>302</v>
       </c>
-      <c r="C50" s="12" t="s">
+      <c r="C50" s="13" t="s">
         <v>353</v>
       </c>
-      <c r="D50" s="13" t="s">
+      <c r="D50" s="14" t="s">
         <v>354</v>
       </c>
-      <c r="E50" s="13" t="s">
+      <c r="E50" s="14" t="s">
         <v>355</v>
       </c>
-      <c r="F50" s="13" t="s">
+      <c r="F50" s="14" t="s">
         <v>356</v>
       </c>
-      <c r="G50" s="13" t="s">
+      <c r="G50" s="14" t="s">
         <v>357</v>
       </c>
-      <c r="H50" s="13" t="s">
+      <c r="H50" s="14" t="s">
         <v>358</v>
       </c>
       <c r="I50" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="J50" s="11" t="s">
+      <c r="J50" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K50" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L50" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="51" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A51" s="16" t="s">
+      <c r="K50" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L50" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="17" t="s">
         <v>359</v>
       </c>
-      <c r="B51" s="17" t="s">
+      <c r="B51" s="18" t="s">
         <v>302</v>
       </c>
-      <c r="C51" s="17" t="s">
+      <c r="C51" s="18" t="s">
         <v>360</v>
       </c>
-      <c r="D51" s="18" t="s">
+      <c r="D51" s="10" t="s">
         <v>361</v>
       </c>
-      <c r="E51" s="18" t="s">
+      <c r="E51" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="F51" s="18" t="s">
+      <c r="F51" s="10" t="s">
         <v>363</v>
       </c>
-      <c r="G51" s="18" t="s">
+      <c r="G51" s="10" t="s">
         <v>364</v>
       </c>
-      <c r="H51" s="18" t="s">
+      <c r="H51" s="10" t="s">
         <v>365</v>
       </c>
       <c r="I51" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="J51" s="16" t="s">
+      <c r="J51" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="K51" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L51" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="52" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A52" s="11" t="s">
+      <c r="K51" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L51" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="12" t="s">
         <v>366</v>
       </c>
-      <c r="B52" s="12" t="s">
+      <c r="B52" s="13" t="s">
         <v>302</v>
       </c>
-      <c r="C52" s="12" t="s">
+      <c r="C52" s="13" t="s">
         <v>367</v>
       </c>
-      <c r="D52" s="13" t="s">
+      <c r="D52" s="14" t="s">
         <v>368</v>
       </c>
-      <c r="E52" s="13" t="s">
+      <c r="E52" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="F52" s="13" t="s">
+      <c r="F52" s="14" t="s">
         <v>369</v>
       </c>
-      <c r="G52" s="13" t="s">
+      <c r="G52" s="14" t="s">
         <v>370</v>
       </c>
-      <c r="H52" s="13" t="s">
+      <c r="H52" s="14" t="s">
         <v>371</v>
       </c>
       <c r="I52" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="J52" s="11" t="s">
+      <c r="J52" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="K52" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L52" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="53" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A53" s="16" t="s">
+      <c r="K52" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L52" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="17" t="s">
         <v>372</v>
       </c>
-      <c r="B53" s="17" t="s">
+      <c r="B53" s="18" t="s">
         <v>373</v>
       </c>
-      <c r="C53" s="17" t="s">
+      <c r="C53" s="18" t="s">
         <v>374</v>
       </c>
-      <c r="D53" s="18" t="s">
+      <c r="D53" s="10" t="s">
         <v>375</v>
       </c>
-      <c r="E53" s="18" t="s">
+      <c r="E53" s="10" t="s">
         <v>376</v>
       </c>
-      <c r="F53" s="18" t="s">
+      <c r="F53" s="10" t="s">
         <v>377</v>
       </c>
-      <c r="G53" s="18" t="s">
+      <c r="G53" s="10" t="s">
         <v>378</v>
       </c>
-      <c r="H53" s="18" t="s">
+      <c r="H53" s="10" t="s">
         <v>379</v>
       </c>
-      <c r="I53" s="14" t="s">
+      <c r="I53" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J53" s="16" t="s">
+      <c r="J53" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="K53" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L53" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="54" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A54" s="11" t="s">
+      <c r="K53" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L53" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="12" t="s">
         <v>380</v>
       </c>
-      <c r="B54" s="12" t="s">
+      <c r="B54" s="13" t="s">
         <v>373</v>
       </c>
-      <c r="C54" s="12" t="s">
+      <c r="C54" s="13" t="s">
         <v>381</v>
       </c>
-      <c r="D54" s="13" t="s">
+      <c r="D54" s="14" t="s">
         <v>382</v>
       </c>
-      <c r="E54" s="13" t="s">
+      <c r="E54" s="14" t="s">
         <v>383</v>
       </c>
-      <c r="F54" s="13" t="s">
+      <c r="F54" s="14" t="s">
         <v>384</v>
       </c>
-      <c r="G54" s="13" t="s">
+      <c r="G54" s="14" t="s">
         <v>385</v>
       </c>
-      <c r="H54" s="13" t="s">
+      <c r="H54" s="14" t="s">
         <v>386</v>
       </c>
-      <c r="I54" s="14" t="s">
+      <c r="I54" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J54" s="11" t="s">
+      <c r="J54" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="K54" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L54" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="55" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A55" s="16" t="s">
+      <c r="K54" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L54" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="17" t="s">
         <v>387</v>
       </c>
-      <c r="B55" s="17" t="s">
+      <c r="B55" s="18" t="s">
         <v>373</v>
       </c>
-      <c r="C55" s="17" t="s">
+      <c r="C55" s="18" t="s">
         <v>388</v>
       </c>
-      <c r="D55" s="18" t="s">
+      <c r="D55" s="10" t="s">
         <v>389</v>
       </c>
-      <c r="E55" s="18" t="s">
+      <c r="E55" s="10" t="s">
         <v>390</v>
       </c>
-      <c r="F55" s="18" t="s">
+      <c r="F55" s="10" t="s">
         <v>391</v>
       </c>
-      <c r="G55" s="18" t="s">
+      <c r="G55" s="10" t="s">
         <v>392</v>
       </c>
-      <c r="H55" s="18" t="s">
+      <c r="H55" s="10" t="s">
         <v>393</v>
       </c>
-      <c r="I55" s="14" t="s">
+      <c r="I55" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J55" s="16" t="s">
+      <c r="J55" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="K55" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L55" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="56" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A56" s="11" t="s">
+      <c r="K55" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L55" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="12" t="s">
         <v>394</v>
       </c>
-      <c r="B56" s="12" t="s">
+      <c r="B56" s="13" t="s">
         <v>373</v>
       </c>
-      <c r="C56" s="12" t="s">
+      <c r="C56" s="13" t="s">
         <v>395</v>
       </c>
-      <c r="D56" s="13" t="s">
+      <c r="D56" s="14" t="s">
         <v>396</v>
       </c>
-      <c r="E56" s="13" t="s">
+      <c r="E56" s="14" t="s">
         <v>390</v>
       </c>
-      <c r="F56" s="13" t="s">
+      <c r="F56" s="14" t="s">
         <v>397</v>
       </c>
-      <c r="G56" s="13" t="s">
+      <c r="G56" s="14" t="s">
         <v>398</v>
       </c>
-      <c r="H56" s="13" t="s">
+      <c r="H56" s="14" t="s">
         <v>393</v>
       </c>
-      <c r="I56" s="14" t="s">
+      <c r="I56" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J56" s="11" t="s">
+      <c r="J56" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="K56" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L56" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="57" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A57" s="16" t="s">
+      <c r="K56" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L56" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="17" t="s">
         <v>399</v>
       </c>
-      <c r="B57" s="17" t="s">
+      <c r="B57" s="18" t="s">
         <v>373</v>
       </c>
-      <c r="C57" s="17" t="s">
+      <c r="C57" s="18" t="s">
         <v>400</v>
       </c>
-      <c r="D57" s="18" t="s">
+      <c r="D57" s="10" t="s">
         <v>401</v>
       </c>
-      <c r="E57" s="18" t="s">
+      <c r="E57" s="10" t="s">
         <v>390</v>
       </c>
-      <c r="F57" s="18" t="s">
+      <c r="F57" s="10" t="s">
         <v>402</v>
       </c>
-      <c r="G57" s="18" t="s">
+      <c r="G57" s="10" t="s">
         <v>403</v>
       </c>
-      <c r="H57" s="18" t="s">
+      <c r="H57" s="10" t="s">
         <v>393</v>
       </c>
-      <c r="I57" s="14" t="s">
+      <c r="I57" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J57" s="16" t="s">
+      <c r="J57" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="K57" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L57" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="58" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A58" s="11" t="s">
+      <c r="K57" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L57" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="12" t="s">
         <v>404</v>
       </c>
-      <c r="B58" s="12" t="s">
+      <c r="B58" s="13" t="s">
         <v>373</v>
       </c>
-      <c r="C58" s="12" t="s">
+      <c r="C58" s="13" t="s">
         <v>405</v>
       </c>
-      <c r="D58" s="13" t="s">
+      <c r="D58" s="14" t="s">
         <v>406</v>
       </c>
-      <c r="E58" s="13" t="s">
+      <c r="E58" s="14" t="s">
         <v>390</v>
       </c>
-      <c r="F58" s="13" t="s">
+      <c r="F58" s="14" t="s">
         <v>407</v>
       </c>
-      <c r="G58" s="13" t="s">
+      <c r="G58" s="14" t="s">
         <v>408</v>
       </c>
-      <c r="H58" s="13" t="s">
+      <c r="H58" s="14" t="s">
         <v>409</v>
       </c>
-      <c r="I58" s="14" t="s">
+      <c r="I58" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J58" s="11" t="s">
+      <c r="J58" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="K58" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L58" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="59" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A59" s="16" t="s">
+      <c r="K58" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L58" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="17" t="s">
         <v>410</v>
       </c>
-      <c r="B59" s="17" t="s">
+      <c r="B59" s="18" t="s">
         <v>373</v>
       </c>
-      <c r="C59" s="17" t="s">
+      <c r="C59" s="18" t="s">
         <v>411</v>
       </c>
-      <c r="D59" s="18" t="s">
+      <c r="D59" s="10" t="s">
         <v>412</v>
       </c>
-      <c r="E59" s="18" t="s">
+      <c r="E59" s="10" t="s">
         <v>413</v>
       </c>
-      <c r="F59" s="18" t="s">
+      <c r="F59" s="10" t="s">
         <v>414</v>
       </c>
-      <c r="G59" s="18" t="s">
+      <c r="G59" s="10" t="s">
         <v>415</v>
       </c>
-      <c r="H59" s="18" t="s">
+      <c r="H59" s="10" t="s">
         <v>416</v>
       </c>
       <c r="I59" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="J59" s="16" t="s">
+      <c r="J59" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="K59" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L59" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="60" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A60" s="11" t="s">
+      <c r="K59" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L59" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="12" t="s">
         <v>417</v>
       </c>
-      <c r="B60" s="12" t="s">
+      <c r="B60" s="13" t="s">
         <v>373</v>
       </c>
-      <c r="C60" s="12" t="s">
+      <c r="C60" s="13" t="s">
         <v>418</v>
       </c>
-      <c r="D60" s="13" t="s">
+      <c r="D60" s="14" t="s">
         <v>419</v>
       </c>
-      <c r="E60" s="13" t="s">
+      <c r="E60" s="14" t="s">
         <v>420</v>
       </c>
-      <c r="F60" s="13" t="s">
+      <c r="F60" s="14" t="s">
         <v>421</v>
       </c>
-      <c r="G60" s="13" t="s">
+      <c r="G60" s="14" t="s">
         <v>422</v>
       </c>
-      <c r="H60" s="13" t="s">
+      <c r="H60" s="14" t="s">
         <v>423</v>
       </c>
       <c r="I60" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="J60" s="11" t="s">
+      <c r="J60" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="K60" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L60" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="61" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A61" s="16" t="s">
+      <c r="K60" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L60" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="17" t="s">
         <v>424</v>
       </c>
-      <c r="B61" s="17" t="s">
+      <c r="B61" s="18" t="s">
         <v>373</v>
       </c>
-      <c r="C61" s="17" t="s">
+      <c r="C61" s="18" t="s">
         <v>425</v>
       </c>
-      <c r="D61" s="18" t="s">
+      <c r="D61" s="10" t="s">
         <v>426</v>
       </c>
-      <c r="E61" s="18" t="s">
+      <c r="E61" s="10" t="s">
         <v>427</v>
       </c>
-      <c r="F61" s="18" t="s">
+      <c r="F61" s="10" t="s">
         <v>428</v>
       </c>
-      <c r="G61" s="18" t="s">
+      <c r="G61" s="10" t="s">
         <v>429</v>
       </c>
-      <c r="H61" s="18" t="s">
+      <c r="H61" s="10" t="s">
         <v>430</v>
       </c>
       <c r="I61" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="J61" s="16" t="s">
+      <c r="J61" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="K61" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L61" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="62" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A62" s="11" t="s">
+      <c r="K61" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L61" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="12" t="s">
         <v>431</v>
       </c>
-      <c r="B62" s="12" t="s">
+      <c r="B62" s="13" t="s">
         <v>432</v>
       </c>
-      <c r="C62" s="12" t="s">
+      <c r="C62" s="13" t="s">
         <v>433</v>
       </c>
-      <c r="D62" s="13" t="s">
+      <c r="D62" s="14" t="s">
         <v>434</v>
       </c>
-      <c r="E62" s="13" t="s">
+      <c r="E62" s="14" t="s">
         <v>435</v>
       </c>
-      <c r="F62" s="13" t="s">
+      <c r="F62" s="14" t="s">
         <v>436</v>
       </c>
-      <c r="G62" s="13" t="s">
+      <c r="G62" s="14" t="s">
         <v>437</v>
       </c>
-      <c r="H62" s="13" t="s">
+      <c r="H62" s="14" t="s">
         <v>438</v>
       </c>
       <c r="I62" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="J62" s="11" t="s">
+      <c r="J62" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="K62" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L62" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="63" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A63" s="16" t="s">
+      <c r="K62" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L62" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="17" t="s">
         <v>439</v>
       </c>
-      <c r="B63" s="17" t="s">
+      <c r="B63" s="18" t="s">
         <v>432</v>
       </c>
-      <c r="C63" s="17" t="s">
+      <c r="C63" s="18" t="s">
         <v>440</v>
       </c>
-      <c r="D63" s="18" t="s">
+      <c r="D63" s="10" t="s">
         <v>441</v>
       </c>
-      <c r="E63" s="18" t="s">
+      <c r="E63" s="10" t="s">
         <v>442</v>
       </c>
-      <c r="F63" s="18" t="s">
+      <c r="F63" s="10" t="s">
         <v>443</v>
       </c>
-      <c r="G63" s="18" t="s">
+      <c r="G63" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="H63" s="18" t="s">
+      <c r="H63" s="10" t="s">
         <v>444</v>
       </c>
-      <c r="I63" s="14" t="s">
+      <c r="I63" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J63" s="16" t="s">
+      <c r="J63" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="K63" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L63" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="64" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A64" s="11" t="s">
+      <c r="K63" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L63" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="12" t="s">
         <v>445</v>
       </c>
-      <c r="B64" s="12" t="s">
+      <c r="B64" s="13" t="s">
         <v>432</v>
       </c>
-      <c r="C64" s="12" t="s">
+      <c r="C64" s="13" t="s">
         <v>446</v>
       </c>
-      <c r="D64" s="13" t="s">
+      <c r="D64" s="14" t="s">
         <v>447</v>
       </c>
-      <c r="E64" s="13" t="s">
+      <c r="E64" s="14" t="s">
         <v>448</v>
       </c>
-      <c r="F64" s="13" t="s">
+      <c r="F64" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="G64" s="13" t="s">
+      <c r="G64" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="H64" s="13" t="s">
+      <c r="H64" s="14" t="s">
         <v>450</v>
       </c>
-      <c r="I64" s="14" t="s">
+      <c r="I64" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J64" s="11" t="s">
+      <c r="J64" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="K64" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L64" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="65" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A65" s="16" t="s">
+      <c r="K64" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L64" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="17" t="s">
         <v>451</v>
       </c>
-      <c r="B65" s="17" t="s">
+      <c r="B65" s="18" t="s">
         <v>432</v>
       </c>
-      <c r="C65" s="17" t="s">
+      <c r="C65" s="18" t="s">
         <v>452</v>
       </c>
-      <c r="D65" s="18" t="s">
+      <c r="D65" s="10" t="s">
         <v>453</v>
       </c>
-      <c r="E65" s="18" t="s">
+      <c r="E65" s="10" t="s">
         <v>448</v>
       </c>
-      <c r="F65" s="18" t="s">
+      <c r="F65" s="10" t="s">
         <v>454</v>
       </c>
-      <c r="G65" s="18" t="s">
+      <c r="G65" s="10" t="s">
         <v>455</v>
       </c>
-      <c r="H65" s="18" t="s">
+      <c r="H65" s="10" t="s">
         <v>456</v>
       </c>
-      <c r="I65" s="14" t="s">
+      <c r="I65" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J65" s="16" t="s">
+      <c r="J65" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="K65" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L65" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="66" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A66" s="11" t="s">
+      <c r="K65" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L65" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="12" t="s">
         <v>457</v>
       </c>
-      <c r="B66" s="12" t="s">
+      <c r="B66" s="13" t="s">
         <v>432</v>
       </c>
-      <c r="C66" s="12" t="s">
+      <c r="C66" s="13" t="s">
         <v>458</v>
       </c>
-      <c r="D66" s="13" t="s">
+      <c r="D66" s="14" t="s">
         <v>459</v>
       </c>
-      <c r="E66" s="13" t="s">
+      <c r="E66" s="14" t="s">
         <v>448</v>
       </c>
-      <c r="F66" s="13" t="s">
+      <c r="F66" s="14" t="s">
         <v>460</v>
       </c>
-      <c r="G66" s="13" t="s">
+      <c r="G66" s="14" t="s">
         <v>461</v>
       </c>
-      <c r="H66" s="13" t="s">
+      <c r="H66" s="14" t="s">
         <v>462</v>
       </c>
-      <c r="I66" s="14" t="s">
+      <c r="I66" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J66" s="11" t="s">
+      <c r="J66" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="K66" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L66" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="67" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A67" s="16" t="s">
+      <c r="K66" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L66" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="17" t="s">
         <v>463</v>
       </c>
-      <c r="B67" s="17" t="s">
+      <c r="B67" s="18" t="s">
         <v>432</v>
       </c>
-      <c r="C67" s="17" t="s">
+      <c r="C67" s="18" t="s">
         <v>464</v>
       </c>
-      <c r="D67" s="18" t="s">
+      <c r="D67" s="10" t="s">
         <v>465</v>
       </c>
-      <c r="E67" s="18" t="s">
+      <c r="E67" s="10" t="s">
         <v>448</v>
       </c>
-      <c r="F67" s="18" t="s">
+      <c r="F67" s="10" t="s">
         <v>466</v>
       </c>
-      <c r="G67" s="18" t="s">
+      <c r="G67" s="10" t="s">
         <v>467</v>
       </c>
-      <c r="H67" s="18" t="s">
+      <c r="H67" s="10" t="s">
         <v>468</v>
       </c>
-      <c r="I67" s="14" t="s">
+      <c r="I67" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J67" s="16" t="s">
+      <c r="J67" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="K67" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L67" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="68" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A68" s="11" t="s">
+      <c r="K67" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L67" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="12" t="s">
         <v>469</v>
       </c>
-      <c r="B68" s="12" t="s">
+      <c r="B68" s="13" t="s">
         <v>432</v>
       </c>
-      <c r="C68" s="12" t="s">
+      <c r="C68" s="13" t="s">
         <v>470</v>
       </c>
-      <c r="D68" s="13" t="s">
+      <c r="D68" s="14" t="s">
         <v>471</v>
       </c>
-      <c r="E68" s="13" t="s">
+      <c r="E68" s="14" t="s">
         <v>448</v>
       </c>
-      <c r="F68" s="13" t="s">
+      <c r="F68" s="14" t="s">
         <v>472</v>
       </c>
-      <c r="G68" s="13" t="s">
+      <c r="G68" s="14" t="s">
         <v>473</v>
       </c>
-      <c r="H68" s="13" t="s">
+      <c r="H68" s="14" t="s">
         <v>474</v>
       </c>
-      <c r="I68" s="14" t="s">
+      <c r="I68" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J68" s="11" t="s">
+      <c r="J68" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="K68" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L68" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="69" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A69" s="16" t="s">
+      <c r="K68" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L68" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="17" t="s">
         <v>475</v>
       </c>
-      <c r="B69" s="17" t="s">
+      <c r="B69" s="18" t="s">
         <v>432</v>
       </c>
-      <c r="C69" s="17" t="s">
+      <c r="C69" s="18" t="s">
         <v>476</v>
       </c>
-      <c r="D69" s="18" t="s">
+      <c r="D69" s="10" t="s">
         <v>477</v>
       </c>
-      <c r="E69" s="18" t="s">
+      <c r="E69" s="10" t="s">
         <v>478</v>
       </c>
-      <c r="F69" s="18" t="s">
+      <c r="F69" s="10" t="s">
         <v>479</v>
       </c>
-      <c r="G69" s="18" t="s">
+      <c r="G69" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="H69" s="18" t="s">
+      <c r="H69" s="10" t="s">
         <v>480</v>
       </c>
       <c r="I69" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="J69" s="16" t="s">
+      <c r="J69" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="K69" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L69" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="70" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A70" s="11" t="s">
+      <c r="K69" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L69" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="12" t="s">
         <v>481</v>
       </c>
-      <c r="B70" s="12" t="s">
+      <c r="B70" s="13" t="s">
         <v>432</v>
       </c>
-      <c r="C70" s="12" t="s">
+      <c r="C70" s="13" t="s">
         <v>482</v>
       </c>
-      <c r="D70" s="13" t="s">
+      <c r="D70" s="14" t="s">
         <v>483</v>
       </c>
-      <c r="E70" s="13" t="s">
+      <c r="E70" s="14" t="s">
         <v>484</v>
       </c>
-      <c r="F70" s="13" t="s">
+      <c r="F70" s="14" t="s">
         <v>485</v>
       </c>
-      <c r="G70" s="13" t="s">
+      <c r="G70" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="H70" s="13" t="s">
+      <c r="H70" s="14" t="s">
         <v>486</v>
       </c>
-      <c r="I70" s="14" t="s">
+      <c r="I70" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J70" s="11" t="s">
+      <c r="J70" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="K70" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L70" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="71" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A71" s="16" t="s">
+      <c r="K70" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L70" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="17" t="s">
         <v>487</v>
       </c>
-      <c r="B71" s="17" t="s">
+      <c r="B71" s="18" t="s">
         <v>432</v>
       </c>
-      <c r="C71" s="17" t="s">
+      <c r="C71" s="18" t="s">
         <v>488</v>
       </c>
-      <c r="D71" s="18" t="s">
+      <c r="D71" s="10" t="s">
         <v>489</v>
       </c>
-      <c r="E71" s="18" t="s">
+      <c r="E71" s="10" t="s">
         <v>490</v>
       </c>
-      <c r="F71" s="18" t="s">
+      <c r="F71" s="10" t="s">
         <v>491</v>
       </c>
-      <c r="G71" s="18" t="s">
+      <c r="G71" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="H71" s="18" t="s">
+      <c r="H71" s="10" t="s">
         <v>492</v>
       </c>
       <c r="I71" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="J71" s="16" t="s">
+      <c r="J71" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="K71" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L71" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="72" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A72" s="11" t="s">
+      <c r="K71" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L71" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="12" t="s">
         <v>493</v>
       </c>
-      <c r="B72" s="12" t="s">
+      <c r="B72" s="13" t="s">
         <v>494</v>
       </c>
-      <c r="C72" s="12" t="s">
+      <c r="C72" s="13" t="s">
         <v>495</v>
       </c>
-      <c r="D72" s="13" t="s">
+      <c r="D72" s="14" t="s">
         <v>496</v>
       </c>
-      <c r="E72" s="13" t="s">
+      <c r="E72" s="14" t="s">
         <v>497</v>
       </c>
-      <c r="F72" s="13" t="s">
+      <c r="F72" s="14" t="s">
         <v>498</v>
       </c>
-      <c r="G72" s="13" t="s">
+      <c r="G72" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="H72" s="13" t="s">
+      <c r="H72" s="14" t="s">
         <v>499</v>
       </c>
-      <c r="I72" s="14" t="s">
+      <c r="I72" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J72" s="11" t="s">
+      <c r="J72" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="K72" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L72" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="73" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A73" s="16" t="s">
+      <c r="K72" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L72" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="17" t="s">
         <v>500</v>
       </c>
-      <c r="B73" s="17" t="s">
+      <c r="B73" s="18" t="s">
         <v>494</v>
       </c>
-      <c r="C73" s="17" t="s">
+      <c r="C73" s="18" t="s">
         <v>501</v>
       </c>
-      <c r="D73" s="18" t="s">
+      <c r="D73" s="10" t="s">
         <v>502</v>
       </c>
-      <c r="E73" s="18" t="s">
+      <c r="E73" s="10" t="s">
         <v>503</v>
       </c>
-      <c r="F73" s="18" t="s">
+      <c r="F73" s="10" t="s">
         <v>504</v>
       </c>
-      <c r="G73" s="18" t="s">
+      <c r="G73" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="H73" s="18" t="s">
+      <c r="H73" s="10" t="s">
         <v>505</v>
       </c>
-      <c r="I73" s="14" t="s">
+      <c r="I73" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J73" s="16" t="s">
+      <c r="J73" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="K73" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L73" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="74" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A74" s="11" t="s">
+      <c r="K73" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L73" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="12" t="s">
         <v>506</v>
       </c>
-      <c r="B74" s="12" t="s">
+      <c r="B74" s="13" t="s">
         <v>494</v>
       </c>
-      <c r="C74" s="12" t="s">
+      <c r="C74" s="13" t="s">
         <v>507</v>
       </c>
-      <c r="D74" s="13" t="s">
+      <c r="D74" s="14" t="s">
         <v>508</v>
       </c>
-      <c r="E74" s="13" t="s">
+      <c r="E74" s="14" t="s">
         <v>503</v>
       </c>
-      <c r="F74" s="13" t="s">
+      <c r="F74" s="14" t="s">
         <v>509</v>
       </c>
-      <c r="G74" s="13" t="s">
+      <c r="G74" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="H74" s="13" t="s">
+      <c r="H74" s="14" t="s">
         <v>510</v>
       </c>
-      <c r="I74" s="14" t="s">
+      <c r="I74" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J74" s="11" t="s">
+      <c r="J74" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="K74" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L74" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="75" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A75" s="16" t="s">
+      <c r="K74" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L74" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="17" t="s">
         <v>511</v>
       </c>
-      <c r="B75" s="17" t="s">
+      <c r="B75" s="18" t="s">
         <v>494</v>
       </c>
-      <c r="C75" s="17" t="s">
+      <c r="C75" s="18" t="s">
         <v>512</v>
       </c>
-      <c r="D75" s="18" t="s">
+      <c r="D75" s="10" t="s">
         <v>513</v>
       </c>
-      <c r="E75" s="18" t="s">
+      <c r="E75" s="10" t="s">
         <v>503</v>
       </c>
-      <c r="F75" s="18" t="s">
+      <c r="F75" s="10" t="s">
         <v>514</v>
       </c>
-      <c r="G75" s="18" t="s">
+      <c r="G75" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="H75" s="18" t="s">
+      <c r="H75" s="10" t="s">
         <v>515</v>
       </c>
-      <c r="I75" s="14" t="s">
+      <c r="I75" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J75" s="16" t="s">
+      <c r="J75" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="K75" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L75" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="76" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A76" s="11" t="s">
+      <c r="K75" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L75" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="12" t="s">
         <v>516</v>
       </c>
-      <c r="B76" s="12" t="s">
+      <c r="B76" s="13" t="s">
         <v>494</v>
       </c>
-      <c r="C76" s="12" t="s">
+      <c r="C76" s="13" t="s">
         <v>517</v>
       </c>
-      <c r="D76" s="13" t="s">
+      <c r="D76" s="14" t="s">
         <v>518</v>
       </c>
-      <c r="E76" s="13" t="s">
+      <c r="E76" s="14" t="s">
         <v>519</v>
       </c>
-      <c r="F76" s="13" t="s">
+      <c r="F76" s="14" t="s">
         <v>520</v>
       </c>
-      <c r="G76" s="13" t="s">
+      <c r="G76" s="14" t="s">
         <v>521</v>
       </c>
-      <c r="H76" s="13" t="s">
+      <c r="H76" s="14" t="s">
         <v>522</v>
       </c>
-      <c r="I76" s="14" t="s">
+      <c r="I76" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J76" s="11" t="s">
+      <c r="J76" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="K76" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L76" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="77" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A77" s="16" t="s">
+      <c r="K76" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L76" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="17" t="s">
         <v>523</v>
       </c>
-      <c r="B77" s="17" t="s">
+      <c r="B77" s="18" t="s">
         <v>524</v>
       </c>
-      <c r="C77" s="17" t="s">
+      <c r="C77" s="18" t="s">
         <v>525</v>
       </c>
-      <c r="D77" s="18" t="s">
+      <c r="D77" s="10" t="s">
         <v>526</v>
       </c>
-      <c r="E77" s="18" t="s">
+      <c r="E77" s="10" t="s">
         <v>527</v>
       </c>
-      <c r="F77" s="18" t="s">
+      <c r="F77" s="10" t="s">
         <v>528</v>
       </c>
-      <c r="G77" s="18" t="s">
+      <c r="G77" s="10" t="s">
         <v>529</v>
       </c>
-      <c r="H77" s="18" t="s">
+      <c r="H77" s="10" t="s">
         <v>530</v>
       </c>
-      <c r="I77" s="14" t="s">
+      <c r="I77" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J77" s="16" t="s">
+      <c r="J77" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="K77" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L77" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="78" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A78" s="11" t="s">
+      <c r="K77" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L77" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="12" t="s">
         <v>531</v>
       </c>
-      <c r="B78" s="12" t="s">
+      <c r="B78" s="13" t="s">
         <v>524</v>
       </c>
-      <c r="C78" s="12" t="s">
+      <c r="C78" s="13" t="s">
         <v>532</v>
       </c>
-      <c r="D78" s="13" t="s">
+      <c r="D78" s="14" t="s">
         <v>533</v>
       </c>
-      <c r="E78" s="13" t="s">
+      <c r="E78" s="14" t="s">
         <v>534</v>
       </c>
-      <c r="F78" s="13" t="s">
+      <c r="F78" s="14" t="s">
         <v>535</v>
       </c>
-      <c r="G78" s="13" t="s">
+      <c r="G78" s="14" t="s">
         <v>536</v>
       </c>
-      <c r="H78" s="13" t="s">
+      <c r="H78" s="14" t="s">
         <v>537</v>
       </c>
-      <c r="I78" s="14" t="s">
+      <c r="I78" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J78" s="11" t="s">
+      <c r="J78" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="K78" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L78" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="79" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A79" s="16" t="s">
+      <c r="K78" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L78" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="17" t="s">
         <v>538</v>
       </c>
-      <c r="B79" s="17" t="s">
+      <c r="B79" s="18" t="s">
         <v>524</v>
       </c>
-      <c r="C79" s="17" t="s">
+      <c r="C79" s="18" t="s">
         <v>539</v>
       </c>
-      <c r="D79" s="18" t="s">
+      <c r="D79" s="10" t="s">
         <v>540</v>
       </c>
-      <c r="E79" s="18" t="s">
+      <c r="E79" s="10" t="s">
         <v>541</v>
       </c>
-      <c r="F79" s="18" t="s">
+      <c r="F79" s="10" t="s">
         <v>542</v>
       </c>
-      <c r="G79" s="18" t="s">
+      <c r="G79" s="10" t="s">
         <v>543</v>
       </c>
-      <c r="H79" s="18" t="s">
+      <c r="H79" s="10" t="s">
         <v>544</v>
       </c>
-      <c r="I79" s="14" t="s">
+      <c r="I79" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J79" s="16" t="s">
+      <c r="J79" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="K79" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L79" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="80" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A80" s="11" t="s">
+      <c r="K79" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L79" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="12" t="s">
         <v>545</v>
       </c>
-      <c r="B80" s="12" t="s">
+      <c r="B80" s="13" t="s">
         <v>524</v>
       </c>
-      <c r="C80" s="12" t="s">
+      <c r="C80" s="13" t="s">
         <v>546</v>
       </c>
-      <c r="D80" s="13" t="s">
+      <c r="D80" s="14" t="s">
         <v>547</v>
       </c>
-      <c r="E80" s="13" t="s">
+      <c r="E80" s="14" t="s">
         <v>548</v>
       </c>
-      <c r="F80" s="13" t="s">
+      <c r="F80" s="14" t="s">
         <v>549</v>
       </c>
-      <c r="G80" s="13" t="s">
+      <c r="G80" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="H80" s="13" t="s">
+      <c r="H80" s="14" t="s">
         <v>550</v>
       </c>
       <c r="I80" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="J80" s="11" t="s">
+      <c r="J80" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="K80" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L80" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="81" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A81" s="16" t="s">
+      <c r="K80" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L80" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="17" t="s">
         <v>551</v>
       </c>
-      <c r="B81" s="17" t="s">
+      <c r="B81" s="18" t="s">
         <v>524</v>
       </c>
-      <c r="C81" s="17" t="s">
+      <c r="C81" s="18" t="s">
         <v>552</v>
       </c>
-      <c r="D81" s="18" t="s">
+      <c r="D81" s="10" t="s">
         <v>553</v>
       </c>
-      <c r="E81" s="18" t="s">
+      <c r="E81" s="10" t="s">
         <v>554</v>
       </c>
-      <c r="F81" s="18" t="s">
+      <c r="F81" s="10" t="s">
         <v>555</v>
       </c>
-      <c r="G81" s="18" t="s">
+      <c r="G81" s="10" t="s">
         <v>556</v>
       </c>
-      <c r="H81" s="18" t="s">
+      <c r="H81" s="10" t="s">
         <v>557</v>
       </c>
-      <c r="I81" s="14" t="s">
+      <c r="I81" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J81" s="16" t="s">
+      <c r="J81" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="K81" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L81" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="82" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A82" s="11" t="s">
+      <c r="K81" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L81" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="12" t="s">
         <v>558</v>
       </c>
-      <c r="B82" s="12" t="s">
+      <c r="B82" s="13" t="s">
         <v>559</v>
       </c>
-      <c r="C82" s="12" t="s">
+      <c r="C82" s="13" t="s">
         <v>560</v>
       </c>
-      <c r="D82" s="13" t="s">
+      <c r="D82" s="14" t="s">
         <v>561</v>
       </c>
-      <c r="E82" s="13" t="s">
+      <c r="E82" s="14" t="s">
         <v>212</v>
       </c>
-      <c r="F82" s="13" t="s">
+      <c r="F82" s="14" t="s">
         <v>562</v>
       </c>
-      <c r="G82" s="13" t="s">
+      <c r="G82" s="14" t="s">
         <v>563</v>
       </c>
-      <c r="H82" s="13" t="s">
+      <c r="H82" s="14" t="s">
         <v>564</v>
       </c>
-      <c r="I82" s="14" t="s">
+      <c r="I82" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J82" s="11" t="s">
+      <c r="J82" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="K82" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L82" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="83" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A83" s="16" t="s">
+      <c r="K82" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L82" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="17" t="s">
         <v>565</v>
       </c>
-      <c r="B83" s="17" t="s">
+      <c r="B83" s="18" t="s">
         <v>559</v>
       </c>
-      <c r="C83" s="17" t="s">
+      <c r="C83" s="18" t="s">
         <v>566</v>
       </c>
-      <c r="D83" s="18" t="s">
+      <c r="D83" s="10" t="s">
         <v>567</v>
       </c>
-      <c r="E83" s="18" t="s">
+      <c r="E83" s="10" t="s">
         <v>568</v>
       </c>
-      <c r="F83" s="18" t="s">
+      <c r="F83" s="10" t="s">
         <v>569</v>
       </c>
-      <c r="G83" s="18" t="s">
+      <c r="G83" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="H83" s="18" t="s">
+      <c r="H83" s="10" t="s">
         <v>570</v>
       </c>
-      <c r="I83" s="14" t="s">
+      <c r="I83" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J83" s="16" t="s">
+      <c r="J83" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="K83" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L83" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="84" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A84" s="11" t="s">
+      <c r="K83" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L83" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="12" t="s">
         <v>571</v>
       </c>
-      <c r="B84" s="12" t="s">
+      <c r="B84" s="13" t="s">
         <v>572</v>
       </c>
-      <c r="C84" s="12" t="s">
+      <c r="C84" s="13" t="s">
         <v>573</v>
       </c>
-      <c r="D84" s="13" t="s">
+      <c r="D84" s="14" t="s">
         <v>574</v>
       </c>
-      <c r="E84" s="13" t="s">
+      <c r="E84" s="14" t="s">
         <v>575</v>
       </c>
-      <c r="F84" s="13" t="s">
+      <c r="F84" s="14" t="s">
         <v>576</v>
       </c>
-      <c r="G84" s="13" t="s">
+      <c r="G84" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="H84" s="13" t="s">
+      <c r="H84" s="14" t="s">
         <v>577</v>
       </c>
       <c r="I84" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="J84" s="11" t="s">
+      <c r="J84" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K84" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L84" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="85" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A85" s="16" t="s">
+      <c r="K84" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L84" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="17" t="s">
         <v>578</v>
       </c>
-      <c r="B85" s="17" t="s">
+      <c r="B85" s="18" t="s">
         <v>572</v>
       </c>
-      <c r="C85" s="17" t="s">
+      <c r="C85" s="18" t="s">
         <v>579</v>
       </c>
-      <c r="D85" s="18" t="s">
+      <c r="D85" s="10" t="s">
         <v>580</v>
       </c>
-      <c r="E85" s="18" t="s">
+      <c r="E85" s="10" t="s">
         <v>581</v>
       </c>
-      <c r="F85" s="18" t="s">
+      <c r="F85" s="10" t="s">
         <v>582</v>
       </c>
-      <c r="G85" s="18" t="s">
+      <c r="G85" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="H85" s="18" t="s">
+      <c r="H85" s="10" t="s">
         <v>583</v>
       </c>
       <c r="I85" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="J85" s="16" t="s">
+      <c r="J85" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="K85" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L85" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="86" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A86" s="11" t="s">
+      <c r="K85" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L85" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="12" t="s">
         <v>584</v>
       </c>
-      <c r="B86" s="12" t="s">
+      <c r="B86" s="13" t="s">
         <v>585</v>
       </c>
-      <c r="C86" s="12" t="s">
+      <c r="C86" s="13" t="s">
         <v>586</v>
       </c>
-      <c r="D86" s="13" t="s">
+      <c r="D86" s="14" t="s">
         <v>587</v>
       </c>
-      <c r="E86" s="13" t="s">
+      <c r="E86" s="14" t="s">
         <v>588</v>
       </c>
-      <c r="F86" s="13" t="s">
+      <c r="F86" s="14" t="s">
         <v>589</v>
       </c>
-      <c r="G86" s="13" t="s">
+      <c r="G86" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="H86" s="13" t="s">
+      <c r="H86" s="14" t="s">
         <v>590</v>
       </c>
       <c r="I86" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="J86" s="11" t="s">
+      <c r="J86" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="K86" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L86" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="87" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A87" s="16" t="s">
+      <c r="K86" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L86" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="17" t="s">
         <v>591</v>
       </c>
-      <c r="B87" s="17" t="s">
+      <c r="B87" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C87" s="17" t="s">
+      <c r="C87" s="18" t="s">
         <v>592</v>
       </c>
-      <c r="D87" s="18" t="s">
+      <c r="D87" s="10" t="s">
         <v>593</v>
       </c>
-      <c r="E87" s="18" t="s">
+      <c r="E87" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F87" s="18" t="s">
+      <c r="F87" s="10" t="s">
         <v>594</v>
       </c>
-      <c r="G87" s="18" t="s">
+      <c r="G87" s="10" t="s">
         <v>595</v>
       </c>
-      <c r="H87" s="18" t="s">
+      <c r="H87" s="10" t="s">
         <v>596</v>
       </c>
-      <c r="I87" s="14" t="s">
+      <c r="I87" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J87" s="16" t="s">
+      <c r="J87" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="K87" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L87" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="88" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A88" s="11" t="s">
+      <c r="K87" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L87" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="12" t="s">
         <v>597</v>
       </c>
-      <c r="B88" s="12" t="s">
+      <c r="B88" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C88" s="12" t="s">
+      <c r="C88" s="13" t="s">
         <v>598</v>
       </c>
-      <c r="D88" s="13" t="s">
+      <c r="D88" s="14" t="s">
         <v>599</v>
       </c>
-      <c r="E88" s="13" t="s">
+      <c r="E88" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="F88" s="13" t="s">
+      <c r="F88" s="14" t="s">
         <v>600</v>
       </c>
-      <c r="G88" s="13" t="s">
+      <c r="G88" s="14" t="s">
         <v>601</v>
       </c>
-      <c r="H88" s="13" t="s">
+      <c r="H88" s="14" t="s">
         <v>602</v>
       </c>
-      <c r="I88" s="14" t="s">
+      <c r="I88" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J88" s="11" t="s">
+      <c r="J88" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K88" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L88" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="89" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A89" s="16" t="s">
+      <c r="K88" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L88" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="17" t="s">
         <v>603</v>
       </c>
-      <c r="B89" s="17" t="s">
+      <c r="B89" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="C89" s="17" t="s">
+      <c r="C89" s="18" t="s">
         <v>604</v>
       </c>
-      <c r="D89" s="18" t="s">
+      <c r="D89" s="10" t="s">
         <v>605</v>
       </c>
-      <c r="E89" s="18" t="s">
+      <c r="E89" s="10" t="s">
         <v>606</v>
       </c>
-      <c r="F89" s="18" t="s">
+      <c r="F89" s="10" t="s">
         <v>607</v>
       </c>
-      <c r="G89" s="18" t="s">
+      <c r="G89" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="H89" s="18" t="s">
+      <c r="H89" s="10" t="s">
         <v>608</v>
       </c>
       <c r="I89" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="J89" s="16" t="s">
+      <c r="J89" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="K89" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L89" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="90" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A90" s="11" t="s">
+      <c r="K89" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L89" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="12" t="s">
         <v>609</v>
       </c>
-      <c r="B90" s="12" t="s">
+      <c r="B90" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C90" s="12" t="s">
+      <c r="C90" s="13" t="s">
         <v>604</v>
       </c>
-      <c r="D90" s="13" t="s">
+      <c r="D90" s="14" t="s">
         <v>610</v>
       </c>
-      <c r="E90" s="13" t="s">
+      <c r="E90" s="14" t="s">
         <v>606</v>
       </c>
-      <c r="F90" s="13" t="s">
+      <c r="F90" s="14" t="s">
         <v>611</v>
       </c>
-      <c r="G90" s="13" t="s">
+      <c r="G90" s="14" t="s">
         <v>612</v>
       </c>
-      <c r="H90" s="13" t="s">
+      <c r="H90" s="14" t="s">
         <v>613</v>
       </c>
       <c r="I90" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="J90" s="11" t="s">
+      <c r="J90" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="K90" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L90" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="91" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A91" s="16" t="s">
+      <c r="K90" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L90" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="17" t="s">
         <v>614</v>
       </c>
-      <c r="B91" s="17" t="s">
+      <c r="B91" s="18" t="s">
         <v>615</v>
       </c>
-      <c r="C91" s="17" t="s">
+      <c r="C91" s="18" t="s">
         <v>616</v>
       </c>
-      <c r="D91" s="18" t="s">
+      <c r="D91" s="10" t="s">
         <v>617</v>
       </c>
-      <c r="E91" s="18" t="s">
+      <c r="E91" s="10" t="s">
         <v>618</v>
       </c>
-      <c r="F91" s="18" t="s">
+      <c r="F91" s="10" t="s">
         <v>619</v>
       </c>
-      <c r="G91" s="18" t="s">
+      <c r="G91" s="10" t="s">
         <v>620</v>
       </c>
-      <c r="H91" s="18" t="s">
+      <c r="H91" s="10" t="s">
         <v>621</v>
       </c>
       <c r="I91" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="J91" s="16" t="s">
+      <c r="J91" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="K91" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L91" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="92" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A92" s="11" t="s">
+      <c r="K91" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L91" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="12" t="s">
         <v>622</v>
       </c>
-      <c r="B92" s="12" t="s">
+      <c r="B92" s="13" t="s">
         <v>615</v>
       </c>
-      <c r="C92" s="12" t="s">
+      <c r="C92" s="13" t="s">
         <v>623</v>
       </c>
-      <c r="D92" s="13" t="s">
+      <c r="D92" s="14" t="s">
         <v>624</v>
       </c>
-      <c r="E92" s="13" t="s">
+      <c r="E92" s="14" t="s">
         <v>625</v>
       </c>
-      <c r="F92" s="13" t="s">
+      <c r="F92" s="14" t="s">
         <v>626</v>
       </c>
-      <c r="G92" s="13" t="s">
+      <c r="G92" s="14" t="s">
         <v>627</v>
       </c>
-      <c r="H92" s="13" t="s">
+      <c r="H92" s="14" t="s">
         <v>628</v>
       </c>
       <c r="I92" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="J92" s="11" t="s">
+      <c r="J92" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="K92" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L92" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="93" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A93" s="16" t="s">
+      <c r="K92" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L92" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="17" t="s">
         <v>629</v>
       </c>
-      <c r="B93" s="17" t="s">
+      <c r="B93" s="18" t="s">
         <v>615</v>
       </c>
-      <c r="C93" s="17" t="s">
+      <c r="C93" s="18" t="s">
         <v>630</v>
       </c>
-      <c r="D93" s="18" t="s">
+      <c r="D93" s="10" t="s">
         <v>631</v>
       </c>
-      <c r="E93" s="18" t="s">
+      <c r="E93" s="10" t="s">
         <v>625</v>
       </c>
-      <c r="F93" s="18" t="s">
+      <c r="F93" s="10" t="s">
         <v>632</v>
       </c>
-      <c r="G93" s="18" t="s">
+      <c r="G93" s="10" t="s">
         <v>633</v>
       </c>
-      <c r="H93" s="18" t="s">
+      <c r="H93" s="10" t="s">
         <v>634</v>
       </c>
       <c r="I93" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="J93" s="16" t="s">
+      <c r="J93" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="K93" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L93" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="94" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A94" s="11" t="s">
+      <c r="K93" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L93" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="12" t="s">
         <v>635</v>
       </c>
-      <c r="B94" s="12" t="s">
+      <c r="B94" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C94" s="12" t="s">
+      <c r="C94" s="13" t="s">
         <v>636</v>
       </c>
-      <c r="D94" s="13" t="s">
+      <c r="D94" s="14" t="s">
         <v>637</v>
       </c>
-      <c r="E94" s="13" t="s">
+      <c r="E94" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="F94" s="13" t="s">
+      <c r="F94" s="14" t="s">
         <v>638</v>
       </c>
-      <c r="G94" s="13" t="s">
+      <c r="G94" s="14" t="s">
         <v>639</v>
       </c>
-      <c r="H94" s="13" t="s">
+      <c r="H94" s="14" t="s">
         <v>640</v>
       </c>
-      <c r="I94" s="14" t="s">
+      <c r="I94" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J94" s="11" t="s">
+      <c r="J94" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="K94" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L94" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="95" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A95" s="16" t="s">
+      <c r="K94" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L94" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="17" t="s">
         <v>641</v>
       </c>
-      <c r="B95" s="17" t="s">
+      <c r="B95" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C95" s="17" t="s">
+      <c r="C95" s="18" t="s">
         <v>642</v>
       </c>
-      <c r="D95" s="18" t="s">
+      <c r="D95" s="10" t="s">
         <v>643</v>
       </c>
-      <c r="E95" s="18" t="s">
+      <c r="E95" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F95" s="18" t="s">
+      <c r="F95" s="10" t="s">
         <v>644</v>
       </c>
-      <c r="G95" s="18" t="s">
+      <c r="G95" s="10" t="s">
         <v>645</v>
       </c>
-      <c r="H95" s="18" t="s">
+      <c r="H95" s="10" t="s">
         <v>646</v>
       </c>
       <c r="I95" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="J95" s="16" t="s">
+      <c r="J95" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="K95" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L95" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="96" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A96" s="11" t="s">
+      <c r="K95" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L95" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="12" t="s">
         <v>647</v>
       </c>
-      <c r="B96" s="12" t="s">
+      <c r="B96" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C96" s="12" t="s">
+      <c r="C96" s="13" t="s">
         <v>648</v>
       </c>
-      <c r="D96" s="13" t="s">
+      <c r="D96" s="14" t="s">
         <v>649</v>
       </c>
-      <c r="E96" s="13" t="s">
+      <c r="E96" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="F96" s="13" t="s">
+      <c r="F96" s="14" t="s">
         <v>650</v>
       </c>
-      <c r="G96" s="13" t="s">
+      <c r="G96" s="14" t="s">
         <v>651</v>
       </c>
-      <c r="H96" s="13" t="s">
+      <c r="H96" s="14" t="s">
         <v>652</v>
       </c>
-      <c r="I96" s="14" t="s">
+      <c r="I96" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J96" s="11" t="s">
+      <c r="J96" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="K96" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L96" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="97" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A97" s="16" t="s">
+      <c r="K96" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L96" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="B97" s="17" t="s">
+      <c r="B97" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C97" s="17" t="s">
+      <c r="C97" s="18" t="s">
         <v>654</v>
       </c>
-      <c r="D97" s="18" t="s">
+      <c r="D97" s="10" t="s">
         <v>655</v>
       </c>
-      <c r="E97" s="18" t="s">
+      <c r="E97" s="10" t="s">
         <v>639</v>
       </c>
-      <c r="F97" s="18" t="s">
+      <c r="F97" s="10" t="s">
         <v>656</v>
       </c>
-      <c r="G97" s="18" t="s">
+      <c r="G97" s="10" t="s">
         <v>639</v>
       </c>
-      <c r="H97" s="18" t="s">
+      <c r="H97" s="10" t="s">
         <v>657</v>
       </c>
-      <c r="I97" s="14" t="s">
+      <c r="I97" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J97" s="16" t="s">
+      <c r="J97" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="K97" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L97" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="98" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A98" s="11" t="s">
+      <c r="K97" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L97" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="12" t="s">
         <v>658</v>
       </c>
-      <c r="B98" s="12" t="s">
+      <c r="B98" s="13" t="s">
         <v>659</v>
       </c>
-      <c r="C98" s="12" t="s">
+      <c r="C98" s="13" t="s">
         <v>660</v>
       </c>
-      <c r="D98" s="13" t="s">
+      <c r="D98" s="14" t="s">
         <v>661</v>
       </c>
-      <c r="E98" s="13" t="s">
+      <c r="E98" s="14" t="s">
         <v>662</v>
       </c>
-      <c r="F98" s="13" t="s">
+      <c r="F98" s="14" t="s">
         <v>663</v>
       </c>
-      <c r="G98" s="13" t="s">
+      <c r="G98" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="H98" s="13" t="s">
+      <c r="H98" s="14" t="s">
         <v>664</v>
       </c>
-      <c r="I98" s="14" t="s">
+      <c r="I98" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J98" s="11" t="s">
+      <c r="J98" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="K98" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L98" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="99" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A99" s="16" t="s">
+      <c r="K98" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L98" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="17" t="s">
         <v>665</v>
       </c>
-      <c r="B99" s="17" t="s">
+      <c r="B99" s="18" t="s">
         <v>659</v>
       </c>
-      <c r="C99" s="17" t="s">
+      <c r="C99" s="18" t="s">
         <v>666</v>
       </c>
-      <c r="D99" s="18" t="s">
+      <c r="D99" s="10" t="s">
         <v>667</v>
       </c>
-      <c r="E99" s="18" t="s">
+      <c r="E99" s="10" t="s">
         <v>668</v>
       </c>
-      <c r="F99" s="18" t="s">
+      <c r="F99" s="10" t="s">
         <v>669</v>
       </c>
-      <c r="G99" s="18" t="s">
+      <c r="G99" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="H99" s="18" t="s">
+      <c r="H99" s="10" t="s">
         <v>670</v>
       </c>
-      <c r="I99" s="14" t="s">
+      <c r="I99" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J99" s="16" t="s">
+      <c r="J99" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="K99" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L99" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="100" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A100" s="11" t="s">
+      <c r="K99" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L99" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="12" t="s">
         <v>671</v>
       </c>
-      <c r="B100" s="12" t="s">
+      <c r="B100" s="13" t="s">
         <v>659</v>
       </c>
-      <c r="C100" s="12" t="s">
+      <c r="C100" s="13" t="s">
         <v>672</v>
       </c>
-      <c r="D100" s="13" t="s">
+      <c r="D100" s="14" t="s">
         <v>673</v>
       </c>
-      <c r="E100" s="13" t="s">
+      <c r="E100" s="14" t="s">
         <v>674</v>
       </c>
-      <c r="F100" s="13" t="s">
+      <c r="F100" s="14" t="s">
         <v>675</v>
       </c>
-      <c r="G100" s="13" t="s">
+      <c r="G100" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="H100" s="13" t="s">
+      <c r="H100" s="14" t="s">
         <v>676</v>
       </c>
-      <c r="I100" s="14" t="s">
+      <c r="I100" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J100" s="11" t="s">
+      <c r="J100" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="K100" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L100" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="101" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A101" s="16" t="s">
+      <c r="K100" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L100" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="17" t="s">
         <v>677</v>
       </c>
-      <c r="B101" s="17" t="s">
+      <c r="B101" s="18" t="s">
         <v>659</v>
       </c>
-      <c r="C101" s="17" t="s">
+      <c r="C101" s="18" t="s">
         <v>678</v>
       </c>
-      <c r="D101" s="18" t="s">
+      <c r="D101" s="10" t="s">
         <v>679</v>
       </c>
-      <c r="E101" s="18" t="s">
+      <c r="E101" s="10" t="s">
         <v>680</v>
       </c>
-      <c r="F101" s="18" t="s">
+      <c r="F101" s="10" t="s">
         <v>681</v>
       </c>
-      <c r="G101" s="18" t="s">
+      <c r="G101" s="10" t="s">
         <v>682</v>
       </c>
-      <c r="H101" s="18" t="s">
+      <c r="H101" s="10" t="s">
         <v>683</v>
       </c>
       <c r="I101" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="J101" s="16" t="s">
+      <c r="J101" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="K101" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L101" s="17" t="s">
+      <c r="K101" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L101" s="18" t="s">
         <v>45</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L101"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
 </worksheet>
 </file>